--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C68436E-2266-4CB9-A8CD-F4BB232AD019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F9203-A353-4089-84DE-C149AFA423A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E204CAF-E277-4386-AFB8-818B724D4096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280AEE7B-8FE3-4055-B9A0-99EBB2A165F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -372,9 +372,6 @@
     <t>ANE TOLOSA</t>
   </si>
   <si>
-    <t>ITAUBAL</t>
-  </si>
-  <si>
     <t>GLENDA FRANKLIN CRUZ</t>
   </si>
   <si>
@@ -451,6 +448,9 @@
   </si>
   <si>
     <t>ADRYELLY SILVA DA SILVA</t>
+  </si>
+  <si>
+    <t>Itaubal</t>
   </si>
 </sst>
 </file>
@@ -1061,10 +1061,10 @@
         <v>49</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>83</v>
@@ -1083,10 +1083,10 @@
         <v>51</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>83</v>
@@ -1105,10 +1105,10 @@
         <v>52</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>83</v>
@@ -1127,10 +1127,10 @@
         <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>83</v>
@@ -1149,10 +1149,10 @@
         <v>54</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>83</v>
@@ -1171,10 +1171,10 @@
         <v>55</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>83</v>
@@ -1193,10 +1193,10 @@
         <v>56</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>83</v>
@@ -1215,10 +1215,10 @@
         <v>57</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>83</v>
@@ -1237,10 +1237,10 @@
         <v>58</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>83</v>
@@ -1259,10 +1259,10 @@
         <v>61</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>83</v>
@@ -1281,10 +1281,10 @@
         <v>62</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>83</v>
@@ -1303,10 +1303,10 @@
         <v>63</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>83</v>
@@ -1325,10 +1325,10 @@
         <v>64</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>83</v>
@@ -1347,10 +1347,10 @@
         <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>83</v>
@@ -1369,10 +1369,10 @@
         <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>83</v>
@@ -1391,10 +1391,10 @@
         <v>67</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>83</v>
@@ -1413,10 +1413,10 @@
         <v>68</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>83</v>
@@ -1435,10 +1435,10 @@
         <v>69</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>83</v>
@@ -1457,10 +1457,10 @@
         <v>70</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>83</v>
@@ -1479,10 +1479,10 @@
         <v>72</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>83</v>
@@ -1501,10 +1501,10 @@
         <v>71</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>83</v>
@@ -1523,10 +1523,10 @@
         <v>73</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>83</v>
@@ -2896,7 +2896,7 @@
         <v>83</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
@@ -2918,7 +2918,7 @@
         <v>83</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -2940,7 +2940,7 @@
         <v>83</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -2962,7 +2962,7 @@
         <v>83</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -2984,7 +2984,7 @@
         <v>83</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -3006,7 +3006,7 @@
         <v>83</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -3028,7 +3028,7 @@
         <v>83</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -3050,7 +3050,7 @@
         <v>83</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -3072,7 +3072,7 @@
         <v>83</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -3082,19 +3082,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="C102" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="E102" s="3" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -3107,13 +3107,13 @@
         <v>7</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>84</v>
@@ -3129,13 +3129,13 @@
         <v>6</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>84</v>
@@ -3151,13 +3151,13 @@
         <v>5</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>84</v>
@@ -3173,13 +3173,13 @@
         <v>4</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>84</v>
@@ -3192,16 +3192,16 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="C107" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>84</v>
@@ -3217,13 +3217,13 @@
         <v>2</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>84</v>
@@ -3239,13 +3239,13 @@
         <v>1</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>84</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>84</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>82</v>
@@ -3289,7 +3289,7 @@
         <v>82</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>84</v>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>82</v>
@@ -3311,7 +3311,7 @@
         <v>82</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>84</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>82</v>
@@ -3333,7 +3333,7 @@
         <v>82</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>84</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>82</v>
@@ -3355,7 +3355,7 @@
         <v>82</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>84</v>
@@ -3368,7 +3368,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>82</v>
@@ -3377,7 +3377,7 @@
         <v>82</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>84</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>82</v>
@@ -3399,7 +3399,7 @@
         <v>82</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>84</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>82</v>
@@ -3421,7 +3421,7 @@
         <v>82</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>84</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>82</v>
@@ -3443,7 +3443,7 @@
         <v>82</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>84</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>82</v>
@@ -3465,7 +3465,7 @@
         <v>82</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>84</v>
@@ -3478,7 +3478,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>82</v>
@@ -3487,7 +3487,7 @@
         <v>82</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>84</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>82</v>
@@ -3509,7 +3509,7 @@
         <v>82</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>84</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>82</v>
@@ -3531,7 +3531,7 @@
         <v>82</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>84</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>82</v>
@@ -3553,7 +3553,7 @@
         <v>82</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>84</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>82</v>
@@ -3575,7 +3575,7 @@
         <v>82</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>84</v>
@@ -3588,7 +3588,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>82</v>
@@ -3597,7 +3597,7 @@
         <v>82</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>84</v>
@@ -3610,7 +3610,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>82</v>
@@ -3619,7 +3619,7 @@
         <v>82</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>84</v>
@@ -3632,7 +3632,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>82</v>
@@ -3641,7 +3641,7 @@
         <v>82</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>84</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>82</v>
@@ -3663,7 +3663,7 @@
         <v>82</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>84</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>82</v>
@@ -3685,7 +3685,7 @@
         <v>82</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>84</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>82</v>
@@ -3707,7 +3707,7 @@
         <v>82</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>84</v>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280AEE7B-8FE3-4055-B9A0-99EBB2A165F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5072AC9-ADF6-4F9B-B0AB-44BB26CB3334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="146">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -451,6 +451,21 @@
   </si>
   <si>
     <t>Itaubal</t>
+  </si>
+  <si>
+    <t>Edson Gomes de Oliveira</t>
+  </si>
+  <si>
+    <t>EDSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON </t>
+  </si>
+  <si>
+    <t>Laranjal do jari</t>
+  </si>
+  <si>
+    <t>Neuraci pereira magno</t>
   </si>
 </sst>
 </file>
@@ -496,7 +511,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -519,11 +534,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -533,6 +559,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -847,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -3718,6 +3748,46 @@
         <v>2</v>
       </c>
     </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H131" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>145</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H132" s="6">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H78">
     <sortCondition ref="E2:E78"/>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5072AC9-ADF6-4F9B-B0AB-44BB26CB3334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E8DB44-C066-4658-9AE1-716AFCFA25BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="5145" yWindow="3360" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="172">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -466,6 +466,84 @@
   </si>
   <si>
     <t>Neuraci pereira magno</t>
+  </si>
+  <si>
+    <t>Lana Furtado</t>
+  </si>
+  <si>
+    <t>Neikson Nicolau</t>
+  </si>
+  <si>
+    <t>Maria da Penha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabiana da Conceição Araújo </t>
+  </si>
+  <si>
+    <t>Sinaria Regina Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciane Souza de Oliveira </t>
+  </si>
+  <si>
+    <t>Cloudiovan Pinheiro Amaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francione Serrão Freitas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celiomar da Luz Silva </t>
+  </si>
+  <si>
+    <t>Ruane Larissa da Trindade Ramos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrid Santos da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Cleiton Luz Da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iasmim da Luz Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzana Dalvis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juciano luz da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suane da Luz silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sibelli Luz Da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sérgio da Luz Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Feber de Oliveira Júnior </t>
+  </si>
+  <si>
+    <t>Suelen  Luz  da Silva</t>
+  </si>
+  <si>
+    <t>Mazagão</t>
+  </si>
+  <si>
+    <t>MARIA DO SOCORRO TEIXEIRA SILVA</t>
+  </si>
+  <si>
+    <t>OSVALDO QUEIROZ DA SILVA</t>
+  </si>
+  <si>
+    <t>PAULO ENUS TEIXEIRA SILVA</t>
+  </si>
+  <si>
+    <t>AYENN TEIXEIRA SILVA</t>
+  </si>
+  <si>
+    <t>Ayenn Teixeira Silva</t>
   </si>
 </sst>
 </file>
@@ -549,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -559,6 +637,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -877,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -3788,6 +3870,486 @@
         <v>7</v>
       </c>
     </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>146</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H133" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>147</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H134" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>148</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H135" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>149</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H136" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>150</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H137" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>151</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H138" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>152</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H139" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>153</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H140" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>154</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H141" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>155</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H142" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>156</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H143" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>157</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H144" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>158</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H145" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>159</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H146" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>160</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H147" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>161</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H148" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>162</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H149" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>163</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H150" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>164</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H151" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>165</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H152" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>167</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H153" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>168</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H154" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>169</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H155" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>170</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H156" s="8">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H78">
     <sortCondition ref="E2:E78"/>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E8DB44-C066-4658-9AE1-716AFCFA25BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA122C41-CC1A-4332-9F50-29CA0F1A6350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="3360" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="2190" yWindow="2475" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="183">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -544,6 +544,39 @@
   </si>
   <si>
     <t>Ayenn Teixeira Silva</t>
+  </si>
+  <si>
+    <t>FERNANDA MONTEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>MARLUCIA QUEIROZ TEIXEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamires Kevelim Barros dos Santos </t>
+  </si>
+  <si>
+    <t>Josimar Silva da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatriz Vitória Souza dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dulcineia Santos da Silva </t>
+  </si>
+  <si>
+    <t>Elizia Maria R. Lopes de Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasmim Silva dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dione Moraes dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enzo Henrique muniz de Castro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Lenilda Silva dos Santos </t>
   </si>
 </sst>
 </file>
@@ -627,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -641,9 +674,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -959,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -3874,19 +3904,19 @@
       <c r="A133" t="s">
         <v>146</v>
       </c>
-      <c r="B133" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C133" s="7" t="s">
+      <c r="B133" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E133" s="8" t="s">
+      <c r="E133" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H133" s="8">
+      <c r="H133" s="6">
         <v>5</v>
       </c>
     </row>
@@ -3894,19 +3924,19 @@
       <c r="A134" t="s">
         <v>147</v>
       </c>
-      <c r="B134" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C134" s="7" t="s">
+      <c r="B134" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H134" s="8">
+      <c r="H134" s="6">
         <v>5</v>
       </c>
     </row>
@@ -3914,19 +3944,19 @@
       <c r="A135" t="s">
         <v>148</v>
       </c>
-      <c r="B135" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C135" s="7" t="s">
+      <c r="B135" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E135" s="8" t="s">
+      <c r="E135" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H135" s="8">
+      <c r="H135" s="6">
         <v>5</v>
       </c>
     </row>
@@ -3934,19 +3964,19 @@
       <c r="A136" t="s">
         <v>149</v>
       </c>
-      <c r="B136" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C136" s="7" t="s">
+      <c r="B136" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E136" s="8" t="s">
+      <c r="E136" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H136" s="8">
+      <c r="H136" s="6">
         <v>5</v>
       </c>
     </row>
@@ -3954,19 +3984,19 @@
       <c r="A137" t="s">
         <v>150</v>
       </c>
-      <c r="B137" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C137" s="7" t="s">
+      <c r="B137" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E137" s="8" t="s">
+      <c r="E137" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H137" s="8">
+      <c r="H137" s="6">
         <v>5</v>
       </c>
     </row>
@@ -3974,19 +4004,19 @@
       <c r="A138" t="s">
         <v>151</v>
       </c>
-      <c r="B138" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C138" s="7" t="s">
+      <c r="B138" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H138" s="8">
+      <c r="H138" s="6">
         <v>5</v>
       </c>
     </row>
@@ -3994,19 +4024,19 @@
       <c r="A139" t="s">
         <v>152</v>
       </c>
-      <c r="B139" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C139" s="7" t="s">
+      <c r="B139" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E139" s="8" t="s">
+      <c r="E139" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H139" s="8">
+      <c r="H139" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4014,19 +4044,19 @@
       <c r="A140" t="s">
         <v>153</v>
       </c>
-      <c r="B140" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C140" s="7" t="s">
+      <c r="B140" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H140" s="8">
+      <c r="H140" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4034,19 +4064,19 @@
       <c r="A141" t="s">
         <v>154</v>
       </c>
-      <c r="B141" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C141" s="7" t="s">
+      <c r="B141" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C141" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E141" s="8" t="s">
+      <c r="E141" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H141" s="8">
+      <c r="H141" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4054,19 +4084,19 @@
       <c r="A142" t="s">
         <v>155</v>
       </c>
-      <c r="B142" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C142" s="7" t="s">
+      <c r="B142" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H142" s="8">
+      <c r="H142" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4074,19 +4104,19 @@
       <c r="A143" t="s">
         <v>156</v>
       </c>
-      <c r="B143" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C143" s="7" t="s">
+      <c r="B143" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C143" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E143" s="8" t="s">
+      <c r="E143" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H143" s="8">
+      <c r="H143" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4094,19 +4124,19 @@
       <c r="A144" t="s">
         <v>157</v>
       </c>
-      <c r="B144" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C144" s="7" t="s">
+      <c r="B144" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C144" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E144" s="8" t="s">
+      <c r="E144" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H144" s="8">
+      <c r="H144" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4114,19 +4144,19 @@
       <c r="A145" t="s">
         <v>158</v>
       </c>
-      <c r="B145" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C145" s="7" t="s">
+      <c r="B145" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C145" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E145" s="8" t="s">
+      <c r="E145" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H145" s="8">
+      <c r="H145" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4134,19 +4164,19 @@
       <c r="A146" t="s">
         <v>159</v>
       </c>
-      <c r="B146" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C146" s="7" t="s">
+      <c r="B146" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H146" s="8">
+      <c r="H146" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4154,19 +4184,19 @@
       <c r="A147" t="s">
         <v>160</v>
       </c>
-      <c r="B147" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C147" s="7" t="s">
+      <c r="B147" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C147" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E147" s="8" t="s">
+      <c r="E147" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H147" s="8">
+      <c r="H147" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4174,19 +4204,19 @@
       <c r="A148" t="s">
         <v>161</v>
       </c>
-      <c r="B148" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C148" s="7" t="s">
+      <c r="B148" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E148" s="8" t="s">
+      <c r="E148" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H148" s="8">
+      <c r="H148" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4194,19 +4224,19 @@
       <c r="A149" t="s">
         <v>162</v>
       </c>
-      <c r="B149" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C149" s="7" t="s">
+      <c r="B149" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E149" s="8" t="s">
+      <c r="E149" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H149" s="8">
+      <c r="H149" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4214,19 +4244,19 @@
       <c r="A150" t="s">
         <v>163</v>
       </c>
-      <c r="B150" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C150" s="7" t="s">
+      <c r="B150" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C150" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H150" s="8">
+      <c r="H150" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4234,19 +4264,19 @@
       <c r="A151" t="s">
         <v>164</v>
       </c>
-      <c r="B151" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C151" s="7" t="s">
+      <c r="B151" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C151" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E151" s="8" t="s">
+      <c r="E151" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H151" s="8">
+      <c r="H151" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4254,19 +4284,19 @@
       <c r="A152" t="s">
         <v>165</v>
       </c>
-      <c r="B152" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C152" s="7" t="s">
+      <c r="B152" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C152" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E152" s="8" t="s">
+      <c r="E152" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H152" s="8">
+      <c r="H152" s="6">
         <v>5</v>
       </c>
     </row>
@@ -4274,19 +4304,19 @@
       <c r="A153" t="s">
         <v>167</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B153" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C153" s="7" t="s">
+      <c r="C153" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H153" s="8">
+      <c r="E153" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H153" s="6">
         <v>2</v>
       </c>
     </row>
@@ -4294,19 +4324,19 @@
       <c r="A154" t="s">
         <v>168</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C154" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E154" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H154" s="8">
+      <c r="E154" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H154" s="6">
         <v>2</v>
       </c>
     </row>
@@ -4314,19 +4344,19 @@
       <c r="A155" t="s">
         <v>169</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="B155" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="C155" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E155" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H155" s="8">
+      <c r="E155" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H155" s="6">
         <v>2</v>
       </c>
     </row>
@@ -4334,19 +4364,239 @@
       <c r="A156" t="s">
         <v>170</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B156" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C156" s="7" t="s">
+      <c r="C156" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E156" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H156" s="8">
+      <c r="E156" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H156" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>172</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H157" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>173</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H158" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>174</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H159" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>175</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H160">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>176</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H161">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>177</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H163">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>179</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>180</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H165">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>181</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H166">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>182</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H167">
         <v>2</v>
       </c>
     </row>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA122C41-CC1A-4332-9F50-29CA0F1A6350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F7BDB7-444A-43DB-B513-EBC365477E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2190" yWindow="2475" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="200">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -577,6 +577,57 @@
   </si>
   <si>
     <t xml:space="preserve">Maria Lenilda Silva dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">maria iracema da silva </t>
+  </si>
+  <si>
+    <t>maria iraci da silva</t>
+  </si>
+  <si>
+    <t>joão da silva costa</t>
+  </si>
+  <si>
+    <t>ocinete pereira da silva</t>
+  </si>
+  <si>
+    <t>juliana pires da silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vaulucio da silva </t>
+  </si>
+  <si>
+    <t>osmandina da silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruan pires da silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">aline santos da silva </t>
+  </si>
+  <si>
+    <t>eliana palmerim costa</t>
+  </si>
+  <si>
+    <t>doriana da silva nunes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itelimira da silva </t>
+  </si>
+  <si>
+    <t>ana claudia da silva de jesus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">josimar silva da silva </t>
+  </si>
+  <si>
+    <t>tamires kevelem barros dos sanots</t>
+  </si>
+  <si>
+    <t>joelma padilha ferreria</t>
+  </si>
+  <si>
+    <t>val</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -4585,10 +4636,10 @@
         <v>182</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>116</v>
@@ -4598,6 +4649,326 @@
       </c>
       <c r="H167">
         <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>183</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H168">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>184</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H169">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>185</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H170">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>186</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H171">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>187</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H172">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>188</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H173">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>189</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H174">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>190</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H175">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>191</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H176">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>192</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H177">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>193</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H178">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>194</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H179">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>195</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H180">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>196</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H181">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>197</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H182">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>198</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H183">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F7BDB7-444A-43DB-B513-EBC365477E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0566C961-13FB-447B-AEF3-F9260AC994E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2190" yWindow="2475" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="224">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -628,6 +628,78 @@
   </si>
   <si>
     <t>val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Barbosa Tolosa </t>
+  </si>
+  <si>
+    <t>Alanna Ani Leal Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>KAUE COSTA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>ANDRESSA RAYANA MACIEL PINHEIRO</t>
+  </si>
+  <si>
+    <t>RAY</t>
+  </si>
+  <si>
+    <t>Amapá</t>
+  </si>
+  <si>
+    <t>ANDREIA MACIEL DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JORGE SANTOS DE LIMA</t>
+  </si>
+  <si>
+    <t>KAROLINE LOPES OLIVEIRA</t>
+  </si>
+  <si>
+    <t>PEDRO PATRICJ MORAES QUINTELA</t>
+  </si>
+  <si>
+    <t>MARIA CAIDETE MELO</t>
+  </si>
+  <si>
+    <t>FRANCIELE MELO SALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCICLEIA ROCHA DOS SANTOS REIS </t>
+  </si>
+  <si>
+    <t>LEILARA FERREIRA DOS REIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LISBELA ISABEL DOS REIS </t>
+  </si>
+  <si>
+    <t>LUCILENE ROCHA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JPÃO VIANA DE LIMA</t>
+  </si>
+  <si>
+    <t>LIDIANE CORDEIRO PENA</t>
+  </si>
+  <si>
+    <t>THYAGO RYAN PENA FARIAS</t>
+  </si>
+  <si>
+    <t>SABRINA CAMPOS CRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE SILVA  DOS SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA DOS SANTOS DA SILVA </t>
+  </si>
+  <si>
+    <t>MARCOS MATEUS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Mel</t>
   </si>
 </sst>
 </file>
@@ -711,7 +783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -725,6 +797,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1040,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -4487,7 +4562,7 @@
       <c r="E159" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H159" s="7">
+      <c r="H159" s="6">
         <v>2</v>
       </c>
     </row>
@@ -4664,7 +4739,7 @@
       <c r="D168" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E168" s="7" t="s">
+      <c r="E168" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H168">
@@ -4684,7 +4759,7 @@
       <c r="D169" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E169" s="7" t="s">
+      <c r="E169" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H169">
@@ -4704,7 +4779,7 @@
       <c r="D170" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E170" s="7" t="s">
+      <c r="E170" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H170">
@@ -4724,7 +4799,7 @@
       <c r="D171" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E171" s="7" t="s">
+      <c r="E171" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H171">
@@ -4744,7 +4819,7 @@
       <c r="D172" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E172" s="7" t="s">
+      <c r="E172" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H172">
@@ -4764,7 +4839,7 @@
       <c r="D173" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E173" s="7" t="s">
+      <c r="E173" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H173">
@@ -4784,7 +4859,7 @@
       <c r="D174" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E174" s="7" t="s">
+      <c r="E174" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H174">
@@ -4804,7 +4879,7 @@
       <c r="D175" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E175" s="7" t="s">
+      <c r="E175" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H175">
@@ -4824,7 +4899,7 @@
       <c r="D176" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E176" s="7" t="s">
+      <c r="E176" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H176">
@@ -4844,7 +4919,7 @@
       <c r="D177" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E177" s="7" t="s">
+      <c r="E177" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H177">
@@ -4864,7 +4939,7 @@
       <c r="D178" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E178" s="7" t="s">
+      <c r="E178" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H178">
@@ -4884,7 +4959,7 @@
       <c r="D179" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E179" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H179">
@@ -4904,7 +4979,7 @@
       <c r="D180" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E180" s="7" t="s">
+      <c r="E180" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H180">
@@ -4924,7 +4999,7 @@
       <c r="D181" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E181" s="7" t="s">
+      <c r="E181" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H181">
@@ -4944,7 +5019,7 @@
       <c r="D182" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E182" s="7" t="s">
+      <c r="E182" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H182">
@@ -4964,11 +5039,431 @@
       <c r="D183" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E183" s="7" t="s">
+      <c r="E183" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H183">
         <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>200</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H184">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>201</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H185">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>202</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H186">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>203</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>206</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>207</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>208</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>209</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>210</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>211</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>212</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>213</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>214</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>215</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>216</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>217</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>218</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>219</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>220</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>221</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E203" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>222</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D204" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E204" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H204">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0566C961-13FB-447B-AEF3-F9260AC994E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402DEB82-A600-4FF9-A298-2641F277314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2190" yWindow="2475" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="262">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -700,6 +700,120 @@
   </si>
   <si>
     <t>Mel</t>
+  </si>
+  <si>
+    <t>Mayara Fernandes da Silva</t>
+  </si>
+  <si>
+    <t>Flávio Rafael Santana Neves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremias Santos Rodrigues </t>
+  </si>
+  <si>
+    <t>Maria Claudete Rocha Melo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paula Tavares de Oliveira </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brayan Davi Quintela da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Patrick Moraes Quintela </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleyse Derielle Melo Quintela </t>
+  </si>
+  <si>
+    <t>Edrio Riquellme Quintela Chermont</t>
+  </si>
+  <si>
+    <t>Maria de Nazaré de Freitas Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edna de Jesus dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keila da Silva Freitas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manoel Raimundo Alves Barbosa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erondina Miranda Cortes </t>
+  </si>
+  <si>
+    <t>Luiz Claudio miranda dos santos</t>
+  </si>
+  <si>
+    <t>Caio Luygui Amoras</t>
+  </si>
+  <si>
+    <t>Brenda Farias da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luiz Kaue Monteiro Barbosa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luane Christiane Costa Gonçalves </t>
+  </si>
+  <si>
+    <t>Flávia Camily Cordeiro da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Paula Figueiredo Corrêia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Gustavo da Silva de Deus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Henrique Rodrigues </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Carolina Pereira Pantoja </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breno Santana da Silva </t>
+  </si>
+  <si>
+    <t>Ezequiel Marques da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasmin Brandão da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellen Cristina Ferreira dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moacir Gomes Santos dos Santos </t>
+  </si>
+  <si>
+    <t>Erika Adriana Cardoso de Souza Barreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José do Socorro Pena da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alana Correia Soares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isabele da Silva Sampaio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Sillas da Silva Chaves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benedito Souza dos Santos </t>
+  </si>
+  <si>
+    <t>Geize de Oliveira Magno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marilena Mendes Monteiro </t>
+  </si>
+  <si>
+    <t>Brenda</t>
   </si>
 </sst>
 </file>
@@ -783,7 +897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -800,7 +914,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1115,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -5050,16 +5163,16 @@
       <c r="A184" t="s">
         <v>200</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C184" s="7" t="s">
+      <c r="C184" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E184" s="8" t="s">
+      <c r="E184" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H184">
@@ -5070,16 +5183,16 @@
       <c r="A185" t="s">
         <v>201</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="B185" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C185" s="7" t="s">
+      <c r="C185" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E185" s="8" t="s">
+      <c r="E185" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H185">
@@ -5090,16 +5203,16 @@
       <c r="A186" t="s">
         <v>202</v>
       </c>
-      <c r="B186" s="7" t="s">
+      <c r="B186" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C186" s="7" t="s">
+      <c r="C186" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E186" s="8" t="s">
+      <c r="E186" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H186">
@@ -5110,16 +5223,16 @@
       <c r="A187" t="s">
         <v>203</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="B187" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C187" s="7" t="s">
+      <c r="C187" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D187" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E187" s="8" t="s">
+      <c r="D187" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E187" s="6" t="s">
         <v>205</v>
       </c>
       <c r="H187">
@@ -5130,16 +5243,16 @@
       <c r="A188" t="s">
         <v>206</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C188" s="7" t="s">
+      <c r="C188" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D188" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E188" s="8" t="s">
+      <c r="D188" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E188" s="6" t="s">
         <v>205</v>
       </c>
       <c r="H188">
@@ -5150,16 +5263,16 @@
       <c r="A189" t="s">
         <v>207</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B189" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C189" s="7" t="s">
+      <c r="C189" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D189" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E189" s="8" t="s">
+      <c r="D189" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E189" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H189">
@@ -5170,16 +5283,16 @@
       <c r="A190" t="s">
         <v>208</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C190" s="7" t="s">
+      <c r="C190" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D190" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E190" s="8" t="s">
+      <c r="D190" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E190" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H190">
@@ -5190,16 +5303,16 @@
       <c r="A191" t="s">
         <v>209</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C191" s="7" t="s">
+      <c r="C191" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D191" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E191" s="8" t="s">
+      <c r="D191" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E191" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H191">
@@ -5210,16 +5323,16 @@
       <c r="A192" t="s">
         <v>210</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B192" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C192" s="7" t="s">
+      <c r="C192" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D192" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E192" s="8" t="s">
+      <c r="D192" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E192" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H192">
@@ -5230,16 +5343,16 @@
       <c r="A193" t="s">
         <v>211</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C193" s="7" t="s">
+      <c r="C193" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D193" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E193" s="8" t="s">
+      <c r="D193" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E193" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H193">
@@ -5250,16 +5363,16 @@
       <c r="A194" t="s">
         <v>212</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="C194" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D194" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E194" s="8" t="s">
+      <c r="D194" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E194" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H194">
@@ -5270,16 +5383,16 @@
       <c r="A195" t="s">
         <v>213</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C195" s="7" t="s">
+      <c r="C195" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D195" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E195" s="8" t="s">
+      <c r="D195" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E195" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H195">
@@ -5290,16 +5403,16 @@
       <c r="A196" t="s">
         <v>214</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B196" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C196" s="7" t="s">
+      <c r="C196" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D196" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E196" s="8" t="s">
+      <c r="D196" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E196" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H196">
@@ -5310,16 +5423,16 @@
       <c r="A197" t="s">
         <v>215</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C197" s="7" t="s">
+      <c r="C197" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D197" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E197" s="8" t="s">
+      <c r="D197" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E197" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H197">
@@ -5330,16 +5443,16 @@
       <c r="A198" t="s">
         <v>216</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C198" s="7" t="s">
+      <c r="C198" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D198" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E198" s="8" t="s">
+      <c r="D198" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E198" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H198">
@@ -5350,16 +5463,16 @@
       <c r="A199" t="s">
         <v>217</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C199" s="7" t="s">
+      <c r="C199" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D199" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E199" s="8" t="s">
+      <c r="D199" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E199" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H199">
@@ -5370,16 +5483,16 @@
       <c r="A200" t="s">
         <v>218</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C200" s="7" t="s">
+      <c r="C200" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E200" s="8" t="s">
+      <c r="D200" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E200" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H200">
@@ -5390,16 +5503,16 @@
       <c r="A201" t="s">
         <v>219</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C201" s="7" t="s">
+      <c r="C201" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D201" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E201" s="8" t="s">
+      <c r="D201" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E201" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H201">
@@ -5410,16 +5523,16 @@
       <c r="A202" t="s">
         <v>220</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C202" s="7" t="s">
+      <c r="C202" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D202" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E202" s="8" t="s">
+      <c r="D202" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E202" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H202">
@@ -5430,16 +5543,16 @@
       <c r="A203" t="s">
         <v>221</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C203" s="7" t="s">
+      <c r="C203" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D203" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E203" s="8" t="s">
+      <c r="D203" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E203" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H203">
@@ -5450,19 +5563,759 @@
       <c r="A204" t="s">
         <v>222</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C204" s="7" t="s">
+      <c r="C204" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D204" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E204" s="8" t="s">
+      <c r="D204" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E204" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>224</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H205">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>225</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>226</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>227</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>228</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>229</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H210">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>230</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>231</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>232</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>233</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>234</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H215">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>235</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>236</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>237</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>238</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>239</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H220">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>240</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>241</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>242</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H223">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>243</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H224">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>244</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H225">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>245</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>246</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H227">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>247</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H228">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>248</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H229">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>249</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>250</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>251</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>252</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>253</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>254</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>255</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H236">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>256</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H237">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>257</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>258</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H239">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>259</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>260</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H241">
         <v>2</v>
       </c>
     </row>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402DEB82-A600-4FF9-A298-2641F277314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97383DE3-FB50-40F1-B539-0FA9C7177855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="2475" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="288">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -814,6 +814,84 @@
   </si>
   <si>
     <t>Brenda</t>
+  </si>
+  <si>
+    <t>Luanna</t>
+  </si>
+  <si>
+    <t>Luanna Gyovanna Farias Gomes</t>
+  </si>
+  <si>
+    <t>Mayane Da Luz de Oliveira</t>
+  </si>
+  <si>
+    <t>Fabian Graziele Nogueira de Oliveira</t>
+  </si>
+  <si>
+    <t>Juliana Farias Ramos</t>
+  </si>
+  <si>
+    <t>Amanda Farias Gomes</t>
+  </si>
+  <si>
+    <t>Peterson Cristian Moura e Silva</t>
+  </si>
+  <si>
+    <t>Daniel Barros dos Santos</t>
+  </si>
+  <si>
+    <t>Cristiana Raiça Piedade Modesto</t>
+  </si>
+  <si>
+    <t>Ydla Aguiar Morais</t>
+  </si>
+  <si>
+    <t>Karina Aguiar Morais</t>
+  </si>
+  <si>
+    <t>Marcilene da Luz de Oliveira</t>
+  </si>
+  <si>
+    <t>Maria Rosinete Lobato da Luz</t>
+  </si>
+  <si>
+    <t>Carla Lidiane Quaresma Farias</t>
+  </si>
+  <si>
+    <t>Wemesson Farias da Silva</t>
+  </si>
+  <si>
+    <t>Antonio Jose Quaresma Filho</t>
+  </si>
+  <si>
+    <t>Francisca Maria Quaresma Farias</t>
+  </si>
+  <si>
+    <t>Ramon Farias Ramos</t>
+  </si>
+  <si>
+    <t>Teresa Farias</t>
+  </si>
+  <si>
+    <t>Laudelina Ferreira Aguiar</t>
+  </si>
+  <si>
+    <t>Wane Cristina Silva Gama</t>
+  </si>
+  <si>
+    <t>Karia Cristina Pinheiro Picanço</t>
+  </si>
+  <si>
+    <t>Mateus de Souza Sales</t>
+  </si>
+  <si>
+    <t>Kaio Cezar dos Santos Abreu</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Flexa Santos</t>
+  </si>
+  <si>
+    <t>Erica de Oliveira Magno</t>
   </si>
 </sst>
 </file>
@@ -897,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -911,9 +989,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1228,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H266"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -5903,10 +5978,10 @@
       <c r="A221" t="s">
         <v>240</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B221" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C221" s="7" t="s">
+      <c r="C221" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D221" s="6" t="s">
@@ -5923,10 +5998,10 @@
       <c r="A222" t="s">
         <v>241</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C222" s="7" t="s">
+      <c r="C222" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D222" s="6" t="s">
@@ -5943,10 +6018,10 @@
       <c r="A223" t="s">
         <v>242</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B223" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C223" s="7" t="s">
+      <c r="C223" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D223" s="6" t="s">
@@ -5963,10 +6038,10 @@
       <c r="A224" t="s">
         <v>243</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C224" s="7" t="s">
+      <c r="C224" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D224" s="6" t="s">
@@ -5983,10 +6058,10 @@
       <c r="A225" t="s">
         <v>244</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C225" s="7" t="s">
+      <c r="C225" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D225" s="6" t="s">
@@ -6003,10 +6078,10 @@
       <c r="A226" t="s">
         <v>245</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C226" s="7" t="s">
+      <c r="C226" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D226" s="6" t="s">
@@ -6023,10 +6098,10 @@
       <c r="A227" t="s">
         <v>246</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C227" s="7" t="s">
+      <c r="C227" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D227" s="6" t="s">
@@ -6043,10 +6118,10 @@
       <c r="A228" t="s">
         <v>247</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C228" s="7" t="s">
+      <c r="C228" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D228" s="6" t="s">
@@ -6063,10 +6138,10 @@
       <c r="A229" t="s">
         <v>248</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C229" s="7" t="s">
+      <c r="C229" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D229" s="6" t="s">
@@ -6083,10 +6158,10 @@
       <c r="A230" t="s">
         <v>249</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C230" s="7" t="s">
+      <c r="C230" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D230" s="6" t="s">
@@ -6103,10 +6178,10 @@
       <c r="A231" t="s">
         <v>250</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C231" s="7" t="s">
+      <c r="C231" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D231" s="6" t="s">
@@ -6123,10 +6198,10 @@
       <c r="A232" t="s">
         <v>251</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C232" s="7" t="s">
+      <c r="C232" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D232" s="6" t="s">
@@ -6143,10 +6218,10 @@
       <c r="A233" t="s">
         <v>252</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C233" s="7" t="s">
+      <c r="C233" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D233" s="6" t="s">
@@ -6163,10 +6238,10 @@
       <c r="A234" t="s">
         <v>253</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C234" s="7" t="s">
+      <c r="C234" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D234" s="6" t="s">
@@ -6183,10 +6258,10 @@
       <c r="A235" t="s">
         <v>254</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C235" s="7" t="s">
+      <c r="C235" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D235" s="6" t="s">
@@ -6203,10 +6278,10 @@
       <c r="A236" t="s">
         <v>255</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C236" s="7" t="s">
+      <c r="C236" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D236" s="6" t="s">
@@ -6223,10 +6298,10 @@
       <c r="A237" t="s">
         <v>256</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C237" s="7" t="s">
+      <c r="C237" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D237" s="6" t="s">
@@ -6243,10 +6318,10 @@
       <c r="A238" t="s">
         <v>257</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="B238" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C238" s="7" t="s">
+      <c r="C238" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D238" s="6" t="s">
@@ -6263,10 +6338,10 @@
       <c r="A239" t="s">
         <v>258</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C239" s="7" t="s">
+      <c r="C239" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D239" s="6" t="s">
@@ -6283,10 +6358,10 @@
       <c r="A240" t="s">
         <v>259</v>
       </c>
-      <c r="B240" s="7" t="s">
+      <c r="B240" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C240" s="7" t="s">
+      <c r="C240" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D240" s="6" t="s">
@@ -6303,10 +6378,10 @@
       <c r="A241" t="s">
         <v>260</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C241" s="7" t="s">
+      <c r="C241" s="5" t="s">
         <v>261</v>
       </c>
       <c r="D241" s="6" t="s">
@@ -6316,6 +6391,506 @@
         <v>84</v>
       </c>
       <c r="H241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>263</v>
+      </c>
+      <c r="B242" t="s">
+        <v>262</v>
+      </c>
+      <c r="C242" t="s">
+        <v>262</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>264</v>
+      </c>
+      <c r="B243" t="s">
+        <v>262</v>
+      </c>
+      <c r="C243" t="s">
+        <v>262</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>265</v>
+      </c>
+      <c r="B244" t="s">
+        <v>262</v>
+      </c>
+      <c r="C244" t="s">
+        <v>262</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H244">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>266</v>
+      </c>
+      <c r="B245" t="s">
+        <v>262</v>
+      </c>
+      <c r="C245" t="s">
+        <v>262</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>267</v>
+      </c>
+      <c r="B246" t="s">
+        <v>262</v>
+      </c>
+      <c r="C246" t="s">
+        <v>262</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>268</v>
+      </c>
+      <c r="B247" t="s">
+        <v>262</v>
+      </c>
+      <c r="C247" t="s">
+        <v>262</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>269</v>
+      </c>
+      <c r="B248" t="s">
+        <v>262</v>
+      </c>
+      <c r="C248" t="s">
+        <v>262</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>270</v>
+      </c>
+      <c r="B249" t="s">
+        <v>262</v>
+      </c>
+      <c r="C249" t="s">
+        <v>262</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>271</v>
+      </c>
+      <c r="B250" t="s">
+        <v>262</v>
+      </c>
+      <c r="C250" t="s">
+        <v>262</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>272</v>
+      </c>
+      <c r="B251" t="s">
+        <v>262</v>
+      </c>
+      <c r="C251" t="s">
+        <v>262</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E251" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>273</v>
+      </c>
+      <c r="B252" t="s">
+        <v>262</v>
+      </c>
+      <c r="C252" t="s">
+        <v>262</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H252">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>274</v>
+      </c>
+      <c r="B253" t="s">
+        <v>262</v>
+      </c>
+      <c r="C253" t="s">
+        <v>262</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H253">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>275</v>
+      </c>
+      <c r="B254" t="s">
+        <v>262</v>
+      </c>
+      <c r="C254" t="s">
+        <v>262</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>276</v>
+      </c>
+      <c r="B255" t="s">
+        <v>262</v>
+      </c>
+      <c r="C255" t="s">
+        <v>262</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>277</v>
+      </c>
+      <c r="B256" t="s">
+        <v>262</v>
+      </c>
+      <c r="C256" t="s">
+        <v>262</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H256">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>278</v>
+      </c>
+      <c r="B257" t="s">
+        <v>262</v>
+      </c>
+      <c r="C257" t="s">
+        <v>262</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>279</v>
+      </c>
+      <c r="B258" t="s">
+        <v>262</v>
+      </c>
+      <c r="C258" t="s">
+        <v>262</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>280</v>
+      </c>
+      <c r="B259" t="s">
+        <v>262</v>
+      </c>
+      <c r="C259" t="s">
+        <v>262</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>281</v>
+      </c>
+      <c r="B260" t="s">
+        <v>262</v>
+      </c>
+      <c r="C260" t="s">
+        <v>262</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>282</v>
+      </c>
+      <c r="B261" t="s">
+        <v>262</v>
+      </c>
+      <c r="C261" t="s">
+        <v>262</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>283</v>
+      </c>
+      <c r="B262" t="s">
+        <v>262</v>
+      </c>
+      <c r="C262" t="s">
+        <v>262</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>284</v>
+      </c>
+      <c r="B263" t="s">
+        <v>262</v>
+      </c>
+      <c r="C263" t="s">
+        <v>262</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>285</v>
+      </c>
+      <c r="B264" t="s">
+        <v>262</v>
+      </c>
+      <c r="C264" t="s">
+        <v>262</v>
+      </c>
+      <c r="D264" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>286</v>
+      </c>
+      <c r="B265" t="s">
+        <v>262</v>
+      </c>
+      <c r="C265" t="s">
+        <v>262</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H265">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>287</v>
+      </c>
+      <c r="B266" t="s">
+        <v>262</v>
+      </c>
+      <c r="C266" t="s">
+        <v>262</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H266">
         <v>2</v>
       </c>
     </row>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97383DE3-FB50-40F1-B539-0FA9C7177855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1DE2C5-719D-434D-8908-D216732433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$275</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="297">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -892,6 +892,33 @@
   </si>
   <si>
     <t>Erica de Oliveira Magno</t>
+  </si>
+  <si>
+    <t>Francidalva de Melo Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omar Glauber de Melo Sales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Franciuei de Melo Sales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francineide de Melo Sales </t>
+  </si>
+  <si>
+    <t>Mizael Aguiar Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francivalda de Melo Sales </t>
+  </si>
+  <si>
+    <t>Otni Frank de Melo Silva</t>
+  </si>
+  <si>
+    <t>Charles de Melo Batista</t>
+  </si>
+  <si>
+    <t>Rodrigo Moura Gouveia</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1002,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -989,6 +1016,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1303,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H266"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -6894,7 +6922,188 @@
         <v>2</v>
       </c>
     </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>288</v>
+      </c>
+      <c r="B267" t="s">
+        <v>223</v>
+      </c>
+      <c r="C267" t="s">
+        <v>223</v>
+      </c>
+      <c r="D267" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E267" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H267">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>289</v>
+      </c>
+      <c r="B268" t="s">
+        <v>223</v>
+      </c>
+      <c r="C268" t="s">
+        <v>223</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E268" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H268">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>290</v>
+      </c>
+      <c r="B269" t="s">
+        <v>223</v>
+      </c>
+      <c r="C269" t="s">
+        <v>223</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E269" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H269">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>291</v>
+      </c>
+      <c r="B270" t="s">
+        <v>223</v>
+      </c>
+      <c r="C270" t="s">
+        <v>223</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E270" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H270">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>292</v>
+      </c>
+      <c r="B271" t="s">
+        <v>223</v>
+      </c>
+      <c r="C271" t="s">
+        <v>223</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E271" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H271">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>293</v>
+      </c>
+      <c r="B272" t="s">
+        <v>223</v>
+      </c>
+      <c r="C272" t="s">
+        <v>223</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E272" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H272">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>294</v>
+      </c>
+      <c r="B273" t="s">
+        <v>223</v>
+      </c>
+      <c r="C273" t="s">
+        <v>223</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E273" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H273">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>295</v>
+      </c>
+      <c r="B274" t="s">
+        <v>223</v>
+      </c>
+      <c r="C274" t="s">
+        <v>223</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E274" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H274">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>296</v>
+      </c>
+      <c r="B275" t="s">
+        <v>223</v>
+      </c>
+      <c r="C275" t="s">
+        <v>223</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E275" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H275">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:H275" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H78">
     <sortCondition ref="E2:E78"/>
   </sortState>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1DE2C5-719D-434D-8908-D216732433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FD9065-542C-4A8A-88CF-EAF6404D8DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="120" yWindow="1350" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="345">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -919,6 +919,150 @@
   </si>
   <si>
     <t>Rodrigo Moura Gouveia</t>
+  </si>
+  <si>
+    <t>Celma do socorro da Costa chagas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteffany Raully chagas Duarte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nahely Nariel Tolosa Marques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raimunda Costa da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heloiza Ferreira da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleice Helena Lopes Rodrigues </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doriana da Silva Nunes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatriz Magno Meireles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itelmira da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriana Silva Nascimento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emyla Raquel Rocha Pimentel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jorge Rodrigues Pereira </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasmin Ramilla Picanço da Costa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ediane Pantoja Almeida de Souza </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Railana Goes de Souza </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jose Freitas Gonçalves </t>
+  </si>
+  <si>
+    <t>PORTO GRANDE</t>
+  </si>
+  <si>
+    <t>Jositelma barreto soares de oliveira</t>
+  </si>
+  <si>
+    <t>ronielson soares de oliviera</t>
+  </si>
+  <si>
+    <t>francisco viana de oliveira</t>
+  </si>
+  <si>
+    <t>geová magno de oliveira</t>
+  </si>
+  <si>
+    <t>francisca pereira da silva</t>
+  </si>
+  <si>
+    <t>leticia dos santos ribeiro</t>
+  </si>
+  <si>
+    <t>francisco dos santos ribeiro</t>
+  </si>
+  <si>
+    <t>maria diolena tenorio da silva</t>
+  </si>
+  <si>
+    <t>jose cardoso da silva</t>
+  </si>
+  <si>
+    <t>edenice dos santos pires</t>
+  </si>
+  <si>
+    <t>alberto duarte soares</t>
+  </si>
+  <si>
+    <t>erisson pablo gomes ribeiro</t>
+  </si>
+  <si>
+    <t>ellen nayara gomes ribeiro</t>
+  </si>
+  <si>
+    <t>denilson souza de souza</t>
+  </si>
+  <si>
+    <t>luvas edielson costa pires</t>
+  </si>
+  <si>
+    <t>elris barbosa ribeiro</t>
+  </si>
+  <si>
+    <t>maria de lourdes da silva gomes</t>
+  </si>
+  <si>
+    <t>franciane silva de souza</t>
+  </si>
+  <si>
+    <t>maria cristina souza da silva</t>
+  </si>
+  <si>
+    <t>jomar da silva tenorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alcione pereira de souza </t>
+  </si>
+  <si>
+    <t>mayro souza tenenorio</t>
+  </si>
+  <si>
+    <t>gleiciane da silva costa</t>
+  </si>
+  <si>
+    <t>alexandre dias ribeiro</t>
+  </si>
+  <si>
+    <t>patricia flexa pereira</t>
+  </si>
+  <si>
+    <t>rosinei da silva texeira</t>
+  </si>
+  <si>
+    <t>angela caroline cardoso silva</t>
+  </si>
+  <si>
+    <t>cleuma da silva carodoso</t>
+  </si>
+  <si>
+    <t>adomar da silva gomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lealdo alves da silva </t>
+  </si>
+  <si>
+    <t>cleber da silva cardoso</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1017,6 +1161,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -6935,7 +7082,7 @@
       <c r="D267" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E267" s="7" t="s">
+      <c r="E267" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H267">
@@ -6955,7 +7102,7 @@
       <c r="D268" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E268" s="7" t="s">
+      <c r="E268" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H268">
@@ -6975,7 +7122,7 @@
       <c r="D269" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E269" s="7" t="s">
+      <c r="E269" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H269">
@@ -6995,7 +7142,7 @@
       <c r="D270" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E270" s="7" t="s">
+      <c r="E270" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H270">
@@ -7015,7 +7162,7 @@
       <c r="D271" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E271" s="7" t="s">
+      <c r="E271" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H271">
@@ -7035,7 +7182,7 @@
       <c r="D272" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E272" s="7" t="s">
+      <c r="E272" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H272">
@@ -7055,7 +7202,7 @@
       <c r="D273" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E273" s="7" t="s">
+      <c r="E273" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H273">
@@ -7075,7 +7222,7 @@
       <c r="D274" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E274" s="7" t="s">
+      <c r="E274" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H274">
@@ -7095,11 +7242,951 @@
       <c r="D275" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E275" s="7" t="s">
+      <c r="E275" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H275">
         <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>297</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E276" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>298</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E277" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>299</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E278" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H278">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>300</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E279" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H279">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>301</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H280">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>302</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E281" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H281">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>303</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E282" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H282">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>304</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E283" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H283">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>305</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E284" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H284">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>306</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E285" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>307</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E286" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H286">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>308</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E287" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H287">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>309</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E288" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H288">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>310</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E289" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H289">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>311</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E290" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H290">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>312</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E291" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H291">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>314</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C292" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E292" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H292">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>315</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C293" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E293" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H293">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>316</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C294" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E294" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H294">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>317</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C295" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E295" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H295">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>318</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C296" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E296" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H296">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>319</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C297" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E297" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H297">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>320</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C298" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E298" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H298">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>321</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C299" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E299" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H299">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>322</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C300" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E300" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H300">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>323</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C301" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E301" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H301">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>324</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C302" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E302" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H302">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>325</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C303" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E303" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H303">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>326</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C304" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H304">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>327</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C305" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H305">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>328</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C306" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H306">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>329</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C307" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H307">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>330</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C308" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E308" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H308">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>331</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C309" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E309" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H309">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>332</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C310" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H310">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>333</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C311" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H311">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>334</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C312" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H312">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>335</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C313" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E313" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H313">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>336</v>
+      </c>
+      <c r="B314" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C314" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E314" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H314">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>337</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H315">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>338</v>
+      </c>
+      <c r="B316" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C316" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H316">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>339</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H317">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>340</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C318" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H318">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>341</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C319" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H319">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>342</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C320" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H320">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>343</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C321" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H321">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>344</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C322" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H322">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FD9065-542C-4A8A-88CF-EAF6404D8DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57875B58-4B49-4FD1-8610-8151300C223E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="1350" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="361">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -1063,6 +1063,54 @@
   </si>
   <si>
     <t>cleber da silva cardoso</t>
+  </si>
+  <si>
+    <t>maria do socorro do nascimento</t>
+  </si>
+  <si>
+    <t>leticia do nascimento barbosa</t>
+  </si>
+  <si>
+    <t>verinaldo guedes de figueiredo</t>
+  </si>
+  <si>
+    <t>hellana medeiros</t>
+  </si>
+  <si>
+    <t>rita cassia souza dos santos</t>
+  </si>
+  <si>
+    <t>marcio vagner feliz</t>
+  </si>
+  <si>
+    <t>fabricio henrique douza dos santos</t>
+  </si>
+  <si>
+    <t>josé geovane cristino</t>
+  </si>
+  <si>
+    <t>yasmim da costa lima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maria lucia gomes de souza </t>
+  </si>
+  <si>
+    <t>maria sousa de almeida</t>
+  </si>
+  <si>
+    <t>jose raimundo balieiro dos reis</t>
+  </si>
+  <si>
+    <t>osvaldo almeida de lima</t>
+  </si>
+  <si>
+    <t>thatiane da silva nobre</t>
+  </si>
+  <si>
+    <t>ilete souza de belieiro</t>
+  </si>
+  <si>
+    <t>Ilete</t>
   </si>
 </sst>
 </file>
@@ -1160,10 +1208,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1478,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:I337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -7262,7 +7310,7 @@
       <c r="D276" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E276" s="7" t="s">
+      <c r="E276" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H276">
@@ -7282,7 +7330,7 @@
       <c r="D277" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E277" s="7" t="s">
+      <c r="E277" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H277">
@@ -7302,7 +7350,7 @@
       <c r="D278" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E278" s="7" t="s">
+      <c r="E278" s="6" t="s">
         <v>313</v>
       </c>
       <c r="H278">
@@ -7322,7 +7370,7 @@
       <c r="D279" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E279" s="7" t="s">
+      <c r="E279" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H279">
@@ -7342,7 +7390,7 @@
       <c r="D280" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E280" s="7" t="s">
+      <c r="E280" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H280">
@@ -7362,7 +7410,7 @@
       <c r="D281" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E281" s="7" t="s">
+      <c r="E281" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H281">
@@ -7382,7 +7430,7 @@
       <c r="D282" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E282" s="7" t="s">
+      <c r="E282" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H282">
@@ -7402,7 +7450,7 @@
       <c r="D283" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E283" s="7" t="s">
+      <c r="E283" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H283">
@@ -7422,7 +7470,7 @@
       <c r="D284" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E284" s="7" t="s">
+      <c r="E284" s="6" t="s">
         <v>74</v>
       </c>
       <c r="H284">
@@ -7442,7 +7490,7 @@
       <c r="D285" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E285" s="7" t="s">
+      <c r="E285" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H285">
@@ -7462,7 +7510,7 @@
       <c r="D286" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E286" s="7" t="s">
+      <c r="E286" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H286">
@@ -7482,7 +7530,7 @@
       <c r="D287" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E287" s="7" t="s">
+      <c r="E287" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H287">
@@ -7502,7 +7550,7 @@
       <c r="D288" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E288" s="7" t="s">
+      <c r="E288" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H288">
@@ -7522,7 +7570,7 @@
       <c r="D289" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E289" s="7" t="s">
+      <c r="E289" s="6" t="s">
         <v>313</v>
       </c>
       <c r="H289">
@@ -7542,7 +7590,7 @@
       <c r="D290" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E290" s="7" t="s">
+      <c r="E290" s="6" t="s">
         <v>166</v>
       </c>
       <c r="H290">
@@ -7562,7 +7610,7 @@
       <c r="D291" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E291" s="7" t="s">
+      <c r="E291" s="6" t="s">
         <v>313</v>
       </c>
       <c r="H291">
@@ -7573,16 +7621,16 @@
       <c r="A292" t="s">
         <v>314</v>
       </c>
-      <c r="B292" s="8" t="s">
+      <c r="B292" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C292" s="8" t="s">
+      <c r="C292" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D292" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E292" s="7" t="s">
+      <c r="E292" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H292">
@@ -7593,16 +7641,16 @@
       <c r="A293" t="s">
         <v>315</v>
       </c>
-      <c r="B293" s="8" t="s">
+      <c r="B293" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C293" s="8" t="s">
+      <c r="C293" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D293" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E293" s="7" t="s">
+      <c r="E293" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H293">
@@ -7613,16 +7661,16 @@
       <c r="A294" t="s">
         <v>316</v>
       </c>
-      <c r="B294" s="8" t="s">
+      <c r="B294" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C294" s="8" t="s">
+      <c r="C294" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D294" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E294" s="7" t="s">
+      <c r="E294" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H294">
@@ -7633,16 +7681,16 @@
       <c r="A295" t="s">
         <v>317</v>
       </c>
-      <c r="B295" s="8" t="s">
+      <c r="B295" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C295" s="8" t="s">
+      <c r="C295" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D295" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E295" s="7" t="s">
+      <c r="E295" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H295">
@@ -7653,16 +7701,16 @@
       <c r="A296" t="s">
         <v>318</v>
       </c>
-      <c r="B296" s="8" t="s">
+      <c r="B296" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C296" s="8" t="s">
+      <c r="C296" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D296" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E296" s="7" t="s">
+      <c r="E296" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H296">
@@ -7673,16 +7721,16 @@
       <c r="A297" t="s">
         <v>319</v>
       </c>
-      <c r="B297" s="8" t="s">
+      <c r="B297" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C297" s="8" t="s">
+      <c r="C297" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D297" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E297" s="7" t="s">
+      <c r="E297" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H297">
@@ -7693,16 +7741,16 @@
       <c r="A298" t="s">
         <v>320</v>
       </c>
-      <c r="B298" s="8" t="s">
+      <c r="B298" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C298" s="8" t="s">
+      <c r="C298" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D298" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E298" s="7" t="s">
+      <c r="E298" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H298">
@@ -7713,16 +7761,16 @@
       <c r="A299" t="s">
         <v>321</v>
       </c>
-      <c r="B299" s="8" t="s">
+      <c r="B299" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C299" s="8" t="s">
+      <c r="C299" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D299" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E299" s="7" t="s">
+      <c r="E299" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H299">
@@ -7733,16 +7781,16 @@
       <c r="A300" t="s">
         <v>322</v>
       </c>
-      <c r="B300" s="8" t="s">
+      <c r="B300" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C300" s="8" t="s">
+      <c r="C300" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D300" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E300" s="7" t="s">
+      <c r="E300" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H300">
@@ -7753,16 +7801,16 @@
       <c r="A301" t="s">
         <v>323</v>
       </c>
-      <c r="B301" s="8" t="s">
+      <c r="B301" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C301" s="8" t="s">
+      <c r="C301" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D301" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E301" s="7" t="s">
+      <c r="E301" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H301">
@@ -7773,16 +7821,16 @@
       <c r="A302" t="s">
         <v>324</v>
       </c>
-      <c r="B302" s="8" t="s">
+      <c r="B302" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C302" s="8" t="s">
+      <c r="C302" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D302" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E302" s="7" t="s">
+      <c r="E302" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H302">
@@ -7793,16 +7841,16 @@
       <c r="A303" t="s">
         <v>325</v>
       </c>
-      <c r="B303" s="8" t="s">
+      <c r="B303" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C303" s="8" t="s">
+      <c r="C303" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D303" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E303" s="7" t="s">
+      <c r="E303" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H303">
@@ -7813,16 +7861,16 @@
       <c r="A304" t="s">
         <v>326</v>
       </c>
-      <c r="B304" s="8" t="s">
+      <c r="B304" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C304" s="8" t="s">
+      <c r="C304" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D304" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E304" s="7" t="s">
+      <c r="E304" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H304">
@@ -7833,16 +7881,16 @@
       <c r="A305" t="s">
         <v>327</v>
       </c>
-      <c r="B305" s="8" t="s">
+      <c r="B305" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C305" s="8" t="s">
+      <c r="C305" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D305" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E305" s="7" t="s">
+      <c r="E305" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H305">
@@ -7853,16 +7901,16 @@
       <c r="A306" t="s">
         <v>328</v>
       </c>
-      <c r="B306" s="8" t="s">
+      <c r="B306" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C306" s="8" t="s">
+      <c r="C306" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D306" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E306" s="7" t="s">
+      <c r="E306" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H306">
@@ -7873,16 +7921,16 @@
       <c r="A307" t="s">
         <v>329</v>
       </c>
-      <c r="B307" s="8" t="s">
+      <c r="B307" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C307" s="8" t="s">
+      <c r="C307" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D307" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E307" s="7" t="s">
+      <c r="E307" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H307">
@@ -7893,16 +7941,16 @@
       <c r="A308" t="s">
         <v>330</v>
       </c>
-      <c r="B308" s="8" t="s">
+      <c r="B308" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C308" s="8" t="s">
+      <c r="C308" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D308" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E308" s="7" t="s">
+      <c r="E308" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H308">
@@ -7913,16 +7961,16 @@
       <c r="A309" t="s">
         <v>331</v>
       </c>
-      <c r="B309" s="8" t="s">
+      <c r="B309" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C309" s="8" t="s">
+      <c r="C309" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D309" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E309" s="7" t="s">
+      <c r="E309" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H309">
@@ -7933,16 +7981,16 @@
       <c r="A310" t="s">
         <v>332</v>
       </c>
-      <c r="B310" s="8" t="s">
+      <c r="B310" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C310" s="8" t="s">
+      <c r="C310" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D310" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E310" s="7" t="s">
+      <c r="E310" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H310">
@@ -7953,16 +8001,16 @@
       <c r="A311" t="s">
         <v>333</v>
       </c>
-      <c r="B311" s="8" t="s">
+      <c r="B311" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C311" s="8" t="s">
+      <c r="C311" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D311" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E311" s="7" t="s">
+      <c r="E311" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H311">
@@ -7973,16 +8021,16 @@
       <c r="A312" t="s">
         <v>334</v>
       </c>
-      <c r="B312" s="8" t="s">
+      <c r="B312" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C312" s="8" t="s">
+      <c r="C312" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D312" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E312" s="7" t="s">
+      <c r="E312" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H312">
@@ -7993,16 +8041,16 @@
       <c r="A313" t="s">
         <v>335</v>
       </c>
-      <c r="B313" s="8" t="s">
+      <c r="B313" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C313" s="8" t="s">
+      <c r="C313" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D313" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E313" s="7" t="s">
+      <c r="E313" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H313">
@@ -8013,16 +8061,16 @@
       <c r="A314" t="s">
         <v>336</v>
       </c>
-      <c r="B314" s="8" t="s">
+      <c r="B314" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C314" s="8" t="s">
+      <c r="C314" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E314" s="7" t="s">
+      <c r="E314" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H314">
@@ -8033,16 +8081,16 @@
       <c r="A315" t="s">
         <v>337</v>
       </c>
-      <c r="B315" s="8" t="s">
+      <c r="B315" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C315" s="8" t="s">
+      <c r="C315" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D315" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E315" s="7" t="s">
+      <c r="E315" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H315">
@@ -8053,16 +8101,16 @@
       <c r="A316" t="s">
         <v>338</v>
       </c>
-      <c r="B316" s="8" t="s">
+      <c r="B316" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C316" s="8" t="s">
+      <c r="C316" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D316" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E316" s="7" t="s">
+      <c r="E316" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H316">
@@ -8073,16 +8121,16 @@
       <c r="A317" t="s">
         <v>339</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C317" s="8" t="s">
+      <c r="C317" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E317" s="7" t="s">
+      <c r="E317" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H317">
@@ -8093,16 +8141,16 @@
       <c r="A318" t="s">
         <v>340</v>
       </c>
-      <c r="B318" s="8" t="s">
+      <c r="B318" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C318" s="8" t="s">
+      <c r="C318" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E318" s="7" t="s">
+      <c r="E318" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H318">
@@ -8113,16 +8161,16 @@
       <c r="A319" t="s">
         <v>341</v>
       </c>
-      <c r="B319" s="8" t="s">
+      <c r="B319" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C319" s="8" t="s">
+      <c r="C319" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E319" s="7" t="s">
+      <c r="E319" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H319">
@@ -8133,60 +8181,390 @@
       <c r="A320" t="s">
         <v>342</v>
       </c>
-      <c r="B320" s="8" t="s">
+      <c r="B320" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C320" s="8" t="s">
+      <c r="C320" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D320" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E320" s="7" t="s">
+      <c r="E320" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H320">
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>343</v>
       </c>
-      <c r="B321" s="8" t="s">
+      <c r="B321" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C321" s="8" t="s">
+      <c r="C321" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D321" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E321" s="7" t="s">
+      <c r="E321" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H321">
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>344</v>
       </c>
-      <c r="B322" s="8" t="s">
+      <c r="B322" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C322" s="8" t="s">
+      <c r="C322" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D322" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E322" s="7" t="s">
+      <c r="E322" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H322">
         <v>7</v>
+      </c>
+      <c r="I322">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>345</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E323" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H323">
+        <v>10</v>
+      </c>
+      <c r="I323">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>346</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E324" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H324">
+        <v>10</v>
+      </c>
+      <c r="I324">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>347</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E325" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H325">
+        <v>2</v>
+      </c>
+      <c r="I325">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>348</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E326" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H326">
+        <v>10</v>
+      </c>
+      <c r="I326">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>349</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E327" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H327">
+        <v>10</v>
+      </c>
+      <c r="I327">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>350</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E328" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H328">
+        <v>10</v>
+      </c>
+      <c r="I328">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>351</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C329" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E329" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H329">
+        <v>10</v>
+      </c>
+      <c r="I329">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>352</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C330" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D330" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E330" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H330">
+        <v>10</v>
+      </c>
+      <c r="I330">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>353</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E331" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H331">
+        <v>10</v>
+      </c>
+      <c r="I331">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>354</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C332" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E332" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H332">
+        <v>10</v>
+      </c>
+      <c r="I332">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>355</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C333" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E333" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H333">
+        <v>10</v>
+      </c>
+      <c r="I333">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>356</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C334" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E334" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H334">
+        <v>10</v>
+      </c>
+      <c r="I334">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>357</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C335" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E335" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H335">
+        <v>10</v>
+      </c>
+      <c r="I335">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>358</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C336" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E336" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H336">
+        <v>14</v>
+      </c>
+      <c r="I336">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57875B58-4B49-4FD1-8610-8151300C223E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5BA795-9F6A-47D6-9A5D-E4AB11E29628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="392">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -1111,6 +1111,99 @@
   </si>
   <si>
     <t>Ilete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guilherme Costa Tolosa </t>
+  </si>
+  <si>
+    <t>Fabrício Tolosa Ramos</t>
+  </si>
+  <si>
+    <t>Emílio Pablo costa Tolosa</t>
+  </si>
+  <si>
+    <t>Iranilson da Silva de Souza</t>
+  </si>
+  <si>
+    <t>Deonaldo Maciel Sarmento</t>
+  </si>
+  <si>
+    <t>Marcilene Neves Pinheiro</t>
+  </si>
+  <si>
+    <t>João Barbosa Tolosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kauê Costa De Almeida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raione Almeida Pessoa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dayse Barbosa Dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Carolina Pantoja Nascimento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodrigo dos Reis Nascimento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirail Belém Da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone De Paula Brito </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Flávia Ameliny Lobato Pantoja </t>
+  </si>
+  <si>
+    <t>Regiane Alves Machado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suely Lobato Dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deibson Dos Reis Leite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thalia Santos Pantoja </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Raimunda Dos Santos Costa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robelino Silva Tolosa </t>
+  </si>
+  <si>
+    <t>Agatha Maly Lobato Pantoja</t>
+  </si>
+  <si>
+    <t>Sabrina Nascimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lorran Junior Santos Nepomuceno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iraercio Tavares Do nascimento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafaela Monteiro Dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antônio Amaral Vieira </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raimunda Monteiro Dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Vieira Dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andriele vieira Dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriela Monteiro Dos Santos </t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:I337"/>
+  <dimension ref="A1:I374"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -8562,9 +8655,878 @@
         <v>198</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>359</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C337" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E337" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H337">
+        <v>10</v>
+      </c>
+      <c r="I337">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>361</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C338" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E338" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H338">
+        <v>10</v>
+      </c>
+      <c r="I338">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>111</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C339" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E339" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H339">
+        <v>10</v>
+      </c>
+      <c r="I339">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>110</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C340" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E340" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H340">
+        <v>10</v>
+      </c>
+      <c r="I340">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>109</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E341" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H341">
+        <v>10</v>
+      </c>
+      <c r="I341">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>362</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C342" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E342" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H342">
+        <v>10</v>
+      </c>
+      <c r="I342">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>363</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E343" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H343">
+        <v>10</v>
+      </c>
+      <c r="I343">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>106</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E344" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H344">
+        <v>10</v>
+      </c>
+      <c r="I344">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>105</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C345" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E345" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H345">
+        <v>10</v>
+      </c>
+      <c r="I345">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>364</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D346" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E346" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H346">
+        <v>10</v>
+      </c>
+      <c r="I346">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>365</v>
+      </c>
+      <c r="B347" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C347" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D347" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E347" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H347">
+        <v>10</v>
+      </c>
+      <c r="I347">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>366</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C348" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E348" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H348">
+        <v>10</v>
+      </c>
+      <c r="I348">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>367</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C349" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E349" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H349">
+        <v>10</v>
+      </c>
+      <c r="I349">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>201</v>
+      </c>
+      <c r="B350" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C350" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D350" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E350" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H350">
+        <v>10</v>
+      </c>
+      <c r="I350">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>368</v>
+      </c>
+      <c r="B351" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C351" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E351" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H351">
+        <v>10</v>
+      </c>
+      <c r="I351">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>369</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C352" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E352" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H352">
+        <v>10</v>
+      </c>
+      <c r="I352">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>370</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C353" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D353" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E353" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H353">
+        <v>10</v>
+      </c>
+      <c r="I353">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>371</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E354" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H354">
+        <v>10</v>
+      </c>
+      <c r="I354">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>372</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E355" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H355">
+        <v>10</v>
+      </c>
+      <c r="I355">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>373</v>
+      </c>
+      <c r="B356" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C356" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E356" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H356">
+        <v>10</v>
+      </c>
+      <c r="I356">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>374</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C357" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E357" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H357">
+        <v>10</v>
+      </c>
+      <c r="I357">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>375</v>
+      </c>
+      <c r="B358" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C358" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E358" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H358">
+        <v>10</v>
+      </c>
+      <c r="I358">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>376</v>
+      </c>
+      <c r="B359" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C359" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E359" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H359">
+        <v>10</v>
+      </c>
+      <c r="I359">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>377</v>
+      </c>
+      <c r="B360" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C360" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E360" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H360">
+        <v>10</v>
+      </c>
+      <c r="I360">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>378</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C361" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D361" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E361" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H361">
+        <v>10</v>
+      </c>
+      <c r="I361">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>379</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C362" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D362" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E362" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H362">
+        <v>10</v>
+      </c>
+      <c r="I362">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>380</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C363" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D363" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E363" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H363">
+        <v>10</v>
+      </c>
+      <c r="I363">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>381</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C364" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D364" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E364" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H364">
+        <v>10</v>
+      </c>
+      <c r="I364">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>382</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D365" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E365" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H365">
+        <v>10</v>
+      </c>
+      <c r="I365">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>383</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D366" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E366" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H366">
+        <v>10</v>
+      </c>
+      <c r="I366">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>384</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D367" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E367" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H367">
+        <v>10</v>
+      </c>
+      <c r="I367">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>385</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D368" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E368" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H368">
+        <v>10</v>
+      </c>
+      <c r="I368">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>386</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C369" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D369" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E369" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H369">
+        <v>10</v>
+      </c>
+      <c r="I369">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>387</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C370" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D370" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E370" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H370">
+        <v>10</v>
+      </c>
+      <c r="I370">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>388</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D371" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E371" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H371">
+        <v>10</v>
+      </c>
+      <c r="I371">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>389</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C372" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E372" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H372">
+        <v>10</v>
+      </c>
+      <c r="I372">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>390</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C373" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D373" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E373" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H373">
+        <v>10</v>
+      </c>
+      <c r="I373">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>391</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E374" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H374">
+        <v>10</v>
+      </c>
+      <c r="I374">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5BA795-9F6A-47D6-9A5D-E4AB11E29628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA437F6-DB7D-47A9-ACCE-2C388DECDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$H$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="412">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -1204,6 +1208,66 @@
   </si>
   <si>
     <t xml:space="preserve">Gabriela Monteiro Dos Santos </t>
+  </si>
+  <si>
+    <t>lilliana gomes cardim</t>
+  </si>
+  <si>
+    <t>ana lucia silva gomes</t>
+  </si>
+  <si>
+    <t>ednéia do nascimento jesus</t>
+  </si>
+  <si>
+    <t>marinaldo de jesus ribeiro</t>
+  </si>
+  <si>
+    <t>edmilson gomes silva</t>
+  </si>
+  <si>
+    <t>dimayara anastacia pinto batista</t>
+  </si>
+  <si>
+    <t>edwilson do carmo santana silva</t>
+  </si>
+  <si>
+    <t>eziele nascimento pantoja</t>
+  </si>
+  <si>
+    <t>leonardo lima gomes</t>
+  </si>
+  <si>
+    <t>erika patricia correa silva</t>
+  </si>
+  <si>
+    <t>tais gomes silva</t>
+  </si>
+  <si>
+    <t>isabelle gomes silva</t>
+  </si>
+  <si>
+    <t>mayara silva gomes</t>
+  </si>
+  <si>
+    <t>enájla dos reis jonas duarte</t>
+  </si>
+  <si>
+    <t>jamaira dos reia jonas duarte</t>
+  </si>
+  <si>
+    <t>elicivaldo dos santos duarte</t>
+  </si>
+  <si>
+    <t>andreza dias gomes</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Contagem de cliente</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1305,6 +1369,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1320,6 +1389,4851 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Suporte" refreshedDate="46296.588252430556" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="390" xr:uid="{87FE605C-F668-458F-8EBE-B9812B8C88B2}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H391" sheet="Planilha1"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="cliente" numFmtId="0">
+      <sharedItems count="377">
+        <s v="Tatiane Moraes dos Santos "/>
+        <s v="Margarida Moraes do nascimento "/>
+        <s v="Maria Antônia Ramos Da Silva "/>
+        <s v="Marciane Moraes dos Santos de Sousa "/>
+        <s v="Sofia Moraes dos Santos "/>
+        <s v="Marcinete Moraes dos Santos "/>
+        <s v="José Maria Moraes dos Santos "/>
+        <s v="Domingos Moraes dos Santos"/>
+        <s v="tamires kevelim barros dos santos"/>
+        <s v="edivania conceição da silva"/>
+        <s v="vitoria conceição da silva"/>
+        <s v="irionilson rodrigues da silva"/>
+        <s v="guilherme linho da silva"/>
+        <s v="tryla barros sobrinho"/>
+        <s v="carlos henrik da silva britto"/>
+        <s v="edivan conceição da silva"/>
+        <s v="adrielly silva da silva"/>
+        <s v="arlete ramos da silva"/>
+        <s v="thainara ramos picanço"/>
+        <s v="alcivane barros da silva"/>
+        <s v="aurea carvalho de almeida "/>
+        <s v="katryny silva da silva"/>
+        <s v="maria jos[é de almeida"/>
+        <s v="taiana palheta de souza"/>
+        <s v="odielton as silva ramos"/>
+        <s v="ana clara do espirito santo"/>
+        <s v="edemar coutinho ramos"/>
+        <s v="bianca borges de oliveira "/>
+        <s v="maria de fatima ramos picanço"/>
+        <s v="paulo guilherme coutinho da silva"/>
+        <s v="antonio Santana lopes"/>
+        <s v="ana maria da silva"/>
+        <s v="darlison Santana"/>
+        <s v="camila rodrigues"/>
+        <s v="david Santana"/>
+        <s v="dhyefferson farias"/>
+        <s v="iracildo willias faria"/>
+        <s v="filipe farias"/>
+        <s v="ediene farias"/>
+        <s v="francimar penha"/>
+        <s v="françuar tolosa"/>
+        <s v="rosilene dos santos"/>
+        <s v="selena farias"/>
+        <s v="rene mendes"/>
+        <s v="marcelo rodrigues"/>
+        <s v="celita dos santos"/>
+        <s v="manoel francisco costa"/>
+        <s v="dorenilson de oliveira"/>
+        <s v="josiane dos santos"/>
+        <s v="valdirene conceição dos santos"/>
+        <s v="rangele vitoria pereira nascimento"/>
+        <s v="susan de azevedo gomes"/>
+        <s v="josivan campos correa"/>
+        <s v="maiara costa souza"/>
+        <s v="mailom campos"/>
+        <s v="idionete tavares de souza"/>
+        <s v="luian souza campos"/>
+        <s v="josue souza mourão"/>
+        <s v="nerivaldo maciel dos santos"/>
+        <s v="elusley rezende campos"/>
+        <s v="rosilene amaral resende"/>
+        <s v="eldclei penha campos"/>
+        <s v="ronaldo penha campos"/>
+        <s v="cristiano da costa campos"/>
+        <s v="ziany de souza santos"/>
+        <s v="lenilton barbosa santos "/>
+        <s v="veldeny oliveira passos"/>
+        <s v="caroline amaral rezende"/>
+        <s v="resenalda barbosa dos santos"/>
+        <s v="zineide dos santos campos"/>
+        <s v="raimundo babosa dos santos"/>
+        <s v="leidieli campos amaral"/>
+        <s v="cristiane penha campos"/>
+        <s v="michel jesus miranda"/>
+        <s v="ledina maciel penha"/>
+        <s v="rosiely maciel campos"/>
+        <s v="maicom maicel campos"/>
+        <s v="eldilei penha campos"/>
+        <s v="cardine amaral resende"/>
+        <s v="rosenalda barbosa dos santos"/>
+        <s v="elvisley resende campos"/>
+        <s v="luan souza campos"/>
+        <s v="eliana costa souza"/>
+        <s v="leucimar maciel pires"/>
+        <s v="ilson tavares souza"/>
+        <s v="vanuza amaral penha"/>
+        <s v="luciane penha souza"/>
+        <s v="josimar pires dos santos"/>
+        <s v="rosilena amaral resende"/>
+        <s v="genival quaresma dos santos"/>
+        <s v="sheila passos amaral"/>
+        <s v="Iranilson da Silva de Souza "/>
+        <s v="Pedro Paulo dos Santos Tavares "/>
+        <s v="Civaldo Pacheco Barbosa "/>
+        <s v="Emílio Pablo costa Tolosa "/>
+        <s v="Fabrício Tolosa Ramos "/>
+        <s v="Jose Rodolfo Dos Santos Tavares"/>
+        <s v="Silviane Tolosa Ramos"/>
+        <s v="Dougla Silva Cardoso"/>
+        <s v="Guilherme Costa Tolosa"/>
+        <s v="GLENDA FRANKLIN CRUZ"/>
+        <s v="Marciane Moraes dos Santos de Sousa"/>
+        <s v="Wellington Lemos nunis "/>
+        <s v="klever luan ferreira Gomes"/>
+        <s v="pétala Ariele Nunes modesto "/>
+        <s v="Nádia Pereira Nunes "/>
+        <s v="Ana melqlen de Souza do Carmo "/>
+        <s v="Adria taila Nunes modesto "/>
+        <s v="Adielton Pereira Nunes "/>
+        <s v="jhessica shirley de Oliveira Silva"/>
+        <s v="Jhennefer shenon de Oliveira Silva"/>
+        <s v="Ágatha jasminy de Oliveira Lima"/>
+        <s v="Márcio Gabriel dos santos ferreira"/>
+        <s v="Nayane Pereira Nunes "/>
+        <s v="Ana Cristina Gama Rodrigues"/>
+        <s v="Eriton Martins pereira"/>
+        <s v="Gleice Kelly Pereira Nunes "/>
+        <s v="Adielson Pereira Nunes"/>
+        <s v="Maria Zenália Ribeiro da Silva "/>
+        <s v="Aldiene Pereira Nunes"/>
+        <s v="Eduardo da Silva Azevedo "/>
+        <s v="Nayara Pereira Nunes"/>
+        <s v="Edson Gomes de Oliveira"/>
+        <s v="Neuraci pereira magno"/>
+        <s v="Lana Furtado"/>
+        <s v="Neikson Nicolau"/>
+        <s v="Maria da Penha"/>
+        <s v="Fabiana da Conceição Araújo "/>
+        <s v="Sinaria Regina Costa"/>
+        <s v="Luciane Souza de Oliveira "/>
+        <s v="Cloudiovan Pinheiro Amaral"/>
+        <s v="Francione Serrão Freitas "/>
+        <s v="Celiomar da Luz Silva "/>
+        <s v="Ruane Larissa da Trindade Ramos"/>
+        <s v="Ingrid Santos da Silva "/>
+        <s v="João Cleiton Luz Da Silva "/>
+        <s v="Iasmim da Luz Silva "/>
+        <s v="Suzana Dalvis "/>
+        <s v="Juciano luz da Silva "/>
+        <s v="Suane da Luz silva "/>
+        <s v="Sibelli Luz Da Silva "/>
+        <s v="Sérgio da Luz Silva "/>
+        <s v="James Feber de Oliveira Júnior "/>
+        <s v="Suelen  Luz  da Silva"/>
+        <s v="MARIA DO SOCORRO TEIXEIRA SILVA"/>
+        <s v="OSVALDO QUEIROZ DA SILVA"/>
+        <s v="PAULO ENUS TEIXEIRA SILVA"/>
+        <s v="AYENN TEIXEIRA SILVA"/>
+        <s v="FERNANDA MONTEIRO DA SILVA"/>
+        <s v="MARLUCIA QUEIROZ TEIXEIRA"/>
+        <s v="Tamires Kevelim Barros dos Santos "/>
+        <s v="Josimar Silva da Silva"/>
+        <s v="Beatriz Vitória Souza dos Santos "/>
+        <s v="Dulcineia Santos da Silva "/>
+        <s v="Elizia Maria R. Lopes de Souza"/>
+        <s v="Yasmim Silva dos Santos "/>
+        <s v="Dione Moraes dos Santos "/>
+        <s v="Enzo Henrique muniz de Castro "/>
+        <s v="Maria Lenilda Silva dos Santos "/>
+        <s v="maria iracema da silva "/>
+        <s v="maria iraci da silva"/>
+        <s v="joão da silva costa"/>
+        <s v="ocinete pereira da silva"/>
+        <s v="juliana pires da silva"/>
+        <s v="vaulucio da silva "/>
+        <s v="osmandina da silva"/>
+        <s v="ruan pires da silva "/>
+        <s v="aline santos da silva "/>
+        <s v="eliana palmerim costa"/>
+        <s v="doriana da silva nunes"/>
+        <s v="itelimira da silva "/>
+        <s v="ana claudia da silva de jesus"/>
+        <s v="josimar silva da silva "/>
+        <s v="tamires kevelem barros dos sanots"/>
+        <s v="joelma padilha ferreria"/>
+        <s v="João Barbosa Tolosa "/>
+        <s v="Alanna Ani Leal Dos Santos Silva"/>
+        <s v="KAUE COSTA DE ALMEIDA"/>
+        <s v="ANDRESSA RAYANA MACIEL PINHEIRO"/>
+        <s v="ANDREIA MACIEL DOS SANTOS"/>
+        <s v="JORGE SANTOS DE LIMA"/>
+        <s v="KAROLINE LOPES OLIVEIRA"/>
+        <s v="PEDRO PATRICJ MORAES QUINTELA"/>
+        <s v="MARIA CAIDETE MELO"/>
+        <s v="FRANCIELE MELO SALES"/>
+        <s v="LUCICLEIA ROCHA DOS SANTOS REIS "/>
+        <s v="LEILARA FERREIRA DOS REIS"/>
+        <s v="LISBELA ISABEL DOS REIS "/>
+        <s v="LUCILENE ROCHA DOS SANTOS"/>
+        <s v="JPÃO VIANA DE LIMA"/>
+        <s v="LIDIANE CORDEIRO PENA"/>
+        <s v="THYAGO RYAN PENA FARIAS"/>
+        <s v="SABRINA CAMPOS CRUZ"/>
+        <s v="FELIPE SILVA  DOS SANTOS "/>
+        <s v="SANDRA DOS SANTOS DA SILVA "/>
+        <s v="MARCOS MATEUS DOS SANTOS"/>
+        <s v="Mayara Fernandes da Silva"/>
+        <s v="Flávio Rafael Santana Neves"/>
+        <s v="Jeremias Santos Rodrigues "/>
+        <s v="Maria Claudete Rocha Melo"/>
+        <s v="Paula Tavares de Oliveira "/>
+        <s v="Brayan Davi Quintela da Silva "/>
+        <s v="Pedro Patrick Moraes Quintela "/>
+        <s v="Cleyse Derielle Melo Quintela "/>
+        <s v="Edrio Riquellme Quintela Chermont"/>
+        <s v="Maria de Nazaré de Freitas Garcia"/>
+        <s v="Edna de Jesus dos Santos "/>
+        <s v="Keila da Silva Freitas "/>
+        <s v="Manoel Raimundo Alves Barbosa "/>
+        <s v="Erondina Miranda Cortes "/>
+        <s v="Luiz Claudio miranda dos santos"/>
+        <s v="Caio Luygui Amoras"/>
+        <s v="Brenda Farias da Silva"/>
+        <s v="Luiz Kaue Monteiro Barbosa "/>
+        <s v="Luane Christiane Costa Gonçalves "/>
+        <s v="Flávia Camily Cordeiro da Silva"/>
+        <s v="Ana Paula Figueiredo Corrêia "/>
+        <s v="João Gustavo da Silva de Deus "/>
+        <s v="Leonardo Henrique Rodrigues "/>
+        <s v="Ana Carolina Pereira Pantoja "/>
+        <s v="Breno Santana da Silva "/>
+        <s v="Ezequiel Marques da Silva"/>
+        <s v="Yasmin Brandão da Silva "/>
+        <s v="Ellen Cristina Ferreira dos Santos "/>
+        <s v="Moacir Gomes Santos dos Santos "/>
+        <s v="Erika Adriana Cardoso de Souza Barreto"/>
+        <s v="José do Socorro Pena da Silva "/>
+        <s v="Alana Correia Soares "/>
+        <s v="Isabele da Silva Sampaio "/>
+        <s v="Samuel Sillas da Silva Chaves "/>
+        <s v="Benedito Souza dos Santos "/>
+        <s v="Geize de Oliveira Magno"/>
+        <s v="Marilena Mendes Monteiro "/>
+        <s v="Luanna Gyovanna Farias Gomes"/>
+        <s v="Mayane Da Luz de Oliveira"/>
+        <s v="Fabian Graziele Nogueira de Oliveira"/>
+        <s v="Juliana Farias Ramos"/>
+        <s v="Amanda Farias Gomes"/>
+        <s v="Peterson Cristian Moura e Silva"/>
+        <s v="Daniel Barros dos Santos"/>
+        <s v="Cristiana Raiça Piedade Modesto"/>
+        <s v="Ydla Aguiar Morais"/>
+        <s v="Karina Aguiar Morais"/>
+        <s v="Marcilene da Luz de Oliveira"/>
+        <s v="Maria Rosinete Lobato da Luz"/>
+        <s v="Carla Lidiane Quaresma Farias"/>
+        <s v="Wemesson Farias da Silva"/>
+        <s v="Antonio Jose Quaresma Filho"/>
+        <s v="Francisca Maria Quaresma Farias"/>
+        <s v="Ramon Farias Ramos"/>
+        <s v="Teresa Farias"/>
+        <s v="Laudelina Ferreira Aguiar"/>
+        <s v="Wane Cristina Silva Gama"/>
+        <s v="Karia Cristina Pinheiro Picanço"/>
+        <s v="Mateus de Souza Sales"/>
+        <s v="Kaio Cezar dos Santos Abreu"/>
+        <s v="Carlos Alberto Flexa Santos"/>
+        <s v="Erica de Oliveira Magno"/>
+        <s v="Francidalva de Melo Sales"/>
+        <s v="Omar Glauber de Melo Sales "/>
+        <s v="José Franciuei de Melo Sales "/>
+        <s v="Francineide de Melo Sales "/>
+        <s v="Mizael Aguiar Souza"/>
+        <s v="Francivalda de Melo Sales "/>
+        <s v="Otni Frank de Melo Silva"/>
+        <s v="Charles de Melo Batista"/>
+        <s v="Rodrigo Moura Gouveia"/>
+        <s v="Celma do socorro da Costa chagas"/>
+        <s v="Esteffany Raully chagas Duarte "/>
+        <s v="Nahely Nariel Tolosa Marques "/>
+        <s v="Raimunda Costa da Silva "/>
+        <s v="Heloiza Ferreira da Silva "/>
+        <s v="Gleice Helena Lopes Rodrigues "/>
+        <s v="Doriana da Silva Nunes "/>
+        <s v="Beatriz Magno Meireles "/>
+        <s v="Itelmira da Silva "/>
+        <s v="Adriana Silva Nascimento "/>
+        <s v="Emyla Raquel Rocha Pimentel "/>
+        <s v="Jorge Rodrigues Pereira "/>
+        <s v="Yasmin Ramilla Picanço da Costa "/>
+        <s v="Ediane Pantoja Almeida de Souza "/>
+        <s v="Railana Goes de Souza "/>
+        <s v="Jose Freitas Gonçalves "/>
+        <s v="Jositelma barreto soares de oliveira"/>
+        <s v="ronielson soares de oliviera"/>
+        <s v="francisco viana de oliveira"/>
+        <s v="geová magno de oliveira"/>
+        <s v="francisca pereira da silva"/>
+        <s v="leticia dos santos ribeiro"/>
+        <s v="francisco dos santos ribeiro"/>
+        <s v="maria diolena tenorio da silva"/>
+        <s v="jose cardoso da silva"/>
+        <s v="edenice dos santos pires"/>
+        <s v="alberto duarte soares"/>
+        <s v="erisson pablo gomes ribeiro"/>
+        <s v="ellen nayara gomes ribeiro"/>
+        <s v="denilson souza de souza"/>
+        <s v="luvas edielson costa pires"/>
+        <s v="elris barbosa ribeiro"/>
+        <s v="maria de lourdes da silva gomes"/>
+        <s v="franciane silva de souza"/>
+        <s v="maria cristina souza da silva"/>
+        <s v="jomar da silva tenorio"/>
+        <s v="alcione pereira de souza "/>
+        <s v="mayro souza tenenorio"/>
+        <s v="gleiciane da silva costa"/>
+        <s v="alexandre dias ribeiro"/>
+        <s v="patricia flexa pereira"/>
+        <s v="rosinei da silva texeira"/>
+        <s v="angela caroline cardoso silva"/>
+        <s v="cleuma da silva carodoso"/>
+        <s v="adomar da silva gomes"/>
+        <s v="lealdo alves da silva "/>
+        <s v="cleber da silva cardoso"/>
+        <s v="maria do socorro do nascimento"/>
+        <s v="leticia do nascimento barbosa"/>
+        <s v="verinaldo guedes de figueiredo"/>
+        <s v="hellana medeiros"/>
+        <s v="rita cassia souza dos santos"/>
+        <s v="marcio vagner feliz"/>
+        <s v="fabricio henrique douza dos santos"/>
+        <s v="josé geovane cristino"/>
+        <s v="yasmim da costa lima"/>
+        <s v="maria lucia gomes de souza "/>
+        <s v="maria sousa de almeida"/>
+        <s v="jose raimundo balieiro dos reis"/>
+        <s v="osvaldo almeida de lima"/>
+        <s v="thatiane da silva nobre"/>
+        <s v="ilete souza de belieiro"/>
+        <s v="Guilherme Costa Tolosa "/>
+        <s v="Fabrício Tolosa Ramos"/>
+        <s v="Emílio Pablo costa Tolosa"/>
+        <s v="Iranilson da Silva de Souza"/>
+        <s v="Deonaldo Maciel Sarmento"/>
+        <s v="Marcilene Neves Pinheiro"/>
+        <s v="João Barbosa Tolosa"/>
+        <s v="Kauê Costa De Almeida "/>
+        <s v="Raione Almeida Pessoa "/>
+        <s v="Dayse Barbosa Dos Santos "/>
+        <s v="Ana Carolina Pantoja Nascimento "/>
+        <s v="Rodrigo dos Reis Nascimento "/>
+        <s v="Mirail Belém Da Silva "/>
+        <s v="Simone De Paula Brito "/>
+        <s v=" Flávia Ameliny Lobato Pantoja "/>
+        <s v="Regiane Alves Machado"/>
+        <s v="Suely Lobato Dos Santos "/>
+        <s v="Deibson Dos Reis Leite "/>
+        <s v="Thalia Santos Pantoja "/>
+        <s v="Maria Raimunda Dos Santos Costa "/>
+        <s v="Robelino Silva Tolosa "/>
+        <s v="Agatha Maly Lobato Pantoja"/>
+        <s v="Sabrina Nascimento"/>
+        <s v=" Lorran Junior Santos Nepomuceno"/>
+        <s v="Iraercio Tavares Do nascimento "/>
+        <s v="Rafaela Monteiro Dos Santos "/>
+        <s v="Antônio Amaral Vieira "/>
+        <s v="Raimunda Monteiro Dos Santos "/>
+        <s v="Ray Vieira Dos Santos "/>
+        <s v="Andriele vieira Dos Santos "/>
+        <s v="Gabriela Monteiro Dos Santos "/>
+        <s v="lilliana gomes cardim"/>
+        <s v="ana lucia silva gomes"/>
+        <s v="ednéia do nascimento jesus"/>
+        <s v="marinaldo de jesus ribeiro"/>
+        <s v="edmilson gomes silva"/>
+        <s v="dimayara anastacia pinto batista"/>
+        <s v="edwilson do carmo santana silva"/>
+        <s v="eziele nascimento pantoja"/>
+        <s v="leonardo lima gomes"/>
+        <s v="erika patricia correa silva"/>
+        <s v="tais gomes silva"/>
+        <s v="isabelle gomes silva"/>
+        <s v="mayara silva gomes"/>
+        <s v="enájla dos reis jonas duarte"/>
+        <s v="jamaira dos reia jonas duarte"/>
+        <s v="elicivaldo dos santos duarte"/>
+        <s v="andreza dias gomes"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Apontador" numFmtId="0">
+      <sharedItems count="13">
+        <s v="FERNANDO SANTOS"/>
+        <s v="ADRYELLY SILVA DA SILVA"/>
+        <s v="ANE TOLOSA"/>
+        <s v="GLENDA"/>
+        <s v="JOSIVAN"/>
+        <s v="EDSON"/>
+        <s v="Ayenn Teixeira Silva"/>
+        <s v="val"/>
+        <s v="RAY"/>
+        <s v="Mel"/>
+        <s v="Brenda"/>
+        <s v="Luanna"/>
+        <s v="Ilete"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name=" atendente" numFmtId="0">
+      <sharedItems count="14">
+        <s v="FERNANDO SANTOS"/>
+        <s v="ADRYELLY SILVA DA SILVA"/>
+        <s v="ANE TOLOSA"/>
+        <s v="GLENDA"/>
+        <s v="JOSIVAN"/>
+        <s v="EDSON "/>
+        <s v="Ayenn Teixeira Silva"/>
+        <s v="val"/>
+        <s v="RAY"/>
+        <s v="Mel"/>
+        <s v="Brenda"/>
+        <s v="Luanna"/>
+        <s v="EDSON"/>
+        <s v="Ilete"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Estado" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="municipio" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Comunidade" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Localidade" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="zona" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="14"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="390">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="74"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="75"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="76"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="77"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="79"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="80"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="82"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="83"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="84"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="85"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="86"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="87"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="89"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="90"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="91"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="95"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="99"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="100"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="101"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="102"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="103"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="104"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="105"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="106"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="107"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="108"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="109"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="110"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="122"/>
+    <x v="5"/>
+    <x v="5"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="123"/>
+    <x v="5"/>
+    <x v="5"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="124"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="125"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="126"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="127"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="128"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="129"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="130"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="131"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="132"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="133"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="134"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="135"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="136"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="137"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="138"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="139"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="140"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="141"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="142"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="143"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="144"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="145"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="146"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="147"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="148"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="149"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="150"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="151"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="152"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="153"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="154"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="155"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="156"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="157"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="158"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="159"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="160"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="161"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="162"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="163"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="164"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="165"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="166"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="167"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="168"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="169"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="170"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="171"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="172"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="173"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="174"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="175"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="176"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="177"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="178"/>
+    <x v="8"/>
+    <x v="8"/>
+    <s v="Ap"/>
+    <s v="Amapá"/>
+    <m/>
+    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="179"/>
+    <x v="8"/>
+    <x v="8"/>
+    <s v="Ap"/>
+    <s v="Amapá"/>
+    <m/>
+    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="180"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="181"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="182"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="183"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="184"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="185"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="186"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="187"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="188"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="189"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="190"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="191"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="192"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="193"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="194"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="195"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="196"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="197"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="198"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="199"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="200"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="201"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="202"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="203"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="204"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="205"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="206"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="207"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="208"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="209"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="210"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="211"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="212"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="213"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="214"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="215"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="216"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="217"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="218"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="219"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="220"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="221"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="222"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="223"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="224"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="225"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="226"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="227"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="228"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="229"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="230"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="231"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="232"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="233"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="234"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="235"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="236"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="237"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="238"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="239"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="240"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="241"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="242"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="243"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="244"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="245"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="246"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="247"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="248"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="249"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="250"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="251"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="252"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="253"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="254"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="255"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="256"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="257"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="258"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="259"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="260"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="261"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="262"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="263"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="264"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="265"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="266"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="267"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="268"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="269"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="PORTO GRANDE"/>
+    <m/>
+    <m/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="270"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="271"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="272"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="273"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="274"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="275"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Santana"/>
+    <m/>
+    <m/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="276"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="277"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="278"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="279"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="280"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="PORTO GRANDE"/>
+    <m/>
+    <m/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="281"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="Mazagão"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="282"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Ap"/>
+    <s v="PORTO GRANDE"/>
+    <m/>
+    <m/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="283"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="284"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="285"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="286"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="287"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="288"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="289"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="290"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="291"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="292"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="293"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="294"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="295"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="296"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="297"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="298"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="299"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="300"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="301"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="302"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="303"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="304"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="305"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="306"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="307"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="308"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="309"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="310"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="311"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="312"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="313"/>
+    <x v="5"/>
+    <x v="12"/>
+    <s v="Ap"/>
+    <s v="Laranjal do jari"/>
+    <m/>
+    <m/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="314"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="315"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="316"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="317"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="318"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="319"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="320"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="321"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="322"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="323"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="324"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="325"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="326"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="327"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="328"/>
+    <x v="12"/>
+    <x v="13"/>
+    <s v="Ap"/>
+    <s v="Macapá"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="329"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="330"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="331"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="332"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="333"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="334"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="335"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="176"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="336"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="337"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="338"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="339"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="340"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="341"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="342"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="343"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="344"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="345"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="346"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="347"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="348"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="349"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="350"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="351"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="352"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="353"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="354"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="355"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="356"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="357"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="358"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="359"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Ap"/>
+    <s v="Itaubal"/>
+    <m/>
+    <m/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="360"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="361"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="362"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="363"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="364"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="365"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="366"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="367"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="368"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="369"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="370"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="371"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="372"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="373"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="374"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="375"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="376"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Ap"/>
+    <s v="Tartarugalzinho"/>
+    <m/>
+    <m/>
+    <n v="8"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8490535A-E6C1-4F41-9EDC-C324212FFB17}" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0">
+      <items count="378">
+        <item x="343"/>
+        <item x="352"/>
+        <item x="117"/>
+        <item x="108"/>
+        <item x="311"/>
+        <item x="107"/>
+        <item x="276"/>
+        <item x="16"/>
+        <item x="111"/>
+        <item x="350"/>
+        <item x="227"/>
+        <item x="176"/>
+        <item x="293"/>
+        <item x="303"/>
+        <item x="19"/>
+        <item x="119"/>
+        <item x="306"/>
+        <item x="167"/>
+        <item x="237"/>
+        <item x="339"/>
+        <item x="219"/>
+        <item x="25"/>
+        <item x="171"/>
+        <item x="114"/>
+        <item x="361"/>
+        <item x="31"/>
+        <item x="106"/>
+        <item x="216"/>
+        <item x="179"/>
+        <item x="178"/>
+        <item x="376"/>
+        <item x="358"/>
+        <item x="309"/>
+        <item x="355"/>
+        <item x="247"/>
+        <item x="30"/>
+        <item x="17"/>
+        <item x="20"/>
+        <item x="147"/>
+        <item x="274"/>
+        <item x="152"/>
+        <item x="230"/>
+        <item x="27"/>
+        <item x="201"/>
+        <item x="212"/>
+        <item x="220"/>
+        <item x="211"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="245"/>
+        <item x="256"/>
+        <item x="14"/>
+        <item x="67"/>
+        <item x="132"/>
+        <item x="45"/>
+        <item x="267"/>
+        <item x="265"/>
+        <item x="93"/>
+        <item x="313"/>
+        <item x="310"/>
+        <item x="203"/>
+        <item x="130"/>
+        <item x="240"/>
+        <item x="72"/>
+        <item x="63"/>
+        <item x="239"/>
+        <item x="32"/>
+        <item x="34"/>
+        <item x="338"/>
+        <item x="346"/>
+        <item x="296"/>
+        <item x="333"/>
+        <item x="35"/>
+        <item x="365"/>
+        <item x="156"/>
+        <item x="7"/>
+        <item x="47"/>
+        <item x="169"/>
+        <item x="273"/>
+        <item x="98"/>
+        <item x="153"/>
+        <item x="26"/>
+        <item x="292"/>
+        <item x="280"/>
+        <item x="38"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="364"/>
+        <item x="206"/>
+        <item x="362"/>
+        <item x="204"/>
+        <item x="122"/>
+        <item x="120"/>
+        <item x="366"/>
+        <item x="61"/>
+        <item x="77"/>
+        <item x="82"/>
+        <item x="168"/>
+        <item x="375"/>
+        <item x="154"/>
+        <item x="223"/>
+        <item x="295"/>
+        <item x="298"/>
+        <item x="59"/>
+        <item x="80"/>
+        <item x="331"/>
+        <item x="94"/>
+        <item x="277"/>
+        <item x="373"/>
+        <item x="157"/>
+        <item x="257"/>
+        <item x="225"/>
+        <item x="369"/>
+        <item x="294"/>
+        <item x="115"/>
+        <item x="209"/>
+        <item x="268"/>
+        <item x="221"/>
+        <item x="367"/>
+        <item x="235"/>
+        <item x="127"/>
+        <item x="320"/>
+        <item x="330"/>
+        <item x="95"/>
+        <item x="193"/>
+        <item x="148"/>
+        <item x="37"/>
+        <item x="215"/>
+        <item x="197"/>
+        <item x="300"/>
+        <item x="258"/>
+        <item x="184"/>
+        <item x="39"/>
+        <item x="261"/>
+        <item x="131"/>
+        <item x="248"/>
+        <item x="287"/>
+        <item x="289"/>
+        <item x="285"/>
+        <item x="263"/>
+        <item x="40"/>
+        <item x="359"/>
+        <item x="231"/>
+        <item x="89"/>
+        <item x="286"/>
+        <item x="272"/>
+        <item x="116"/>
+        <item x="305"/>
+        <item x="100"/>
+        <item x="99"/>
+        <item x="329"/>
+        <item x="12"/>
+        <item x="317"/>
+        <item x="271"/>
+        <item x="136"/>
+        <item x="55"/>
+        <item x="328"/>
+        <item x="84"/>
+        <item x="134"/>
+        <item x="36"/>
+        <item x="353"/>
+        <item x="332"/>
+        <item x="91"/>
+        <item x="11"/>
+        <item x="228"/>
+        <item x="371"/>
+        <item x="170"/>
+        <item x="275"/>
+        <item x="374"/>
+        <item x="142"/>
+        <item x="198"/>
+        <item x="110"/>
+        <item x="109"/>
+        <item x="335"/>
+        <item x="175"/>
+        <item x="135"/>
+        <item x="161"/>
+        <item x="217"/>
+        <item x="174"/>
+        <item x="302"/>
+        <item x="278"/>
+        <item x="180"/>
+        <item x="291"/>
+        <item x="226"/>
+        <item x="260"/>
+        <item x="282"/>
+        <item x="321"/>
+        <item x="6"/>
+        <item x="325"/>
+        <item x="96"/>
+        <item x="48"/>
+        <item x="87"/>
+        <item x="151"/>
+        <item x="172"/>
+        <item x="283"/>
+        <item x="52"/>
+        <item x="57"/>
+        <item x="189"/>
+        <item x="138"/>
+        <item x="236"/>
+        <item x="163"/>
+        <item x="255"/>
+        <item x="253"/>
+        <item x="242"/>
+        <item x="181"/>
+        <item x="21"/>
+        <item x="177"/>
+        <item x="336"/>
+        <item x="207"/>
+        <item x="103"/>
+        <item x="124"/>
+        <item x="251"/>
+        <item x="312"/>
+        <item x="74"/>
+        <item x="71"/>
+        <item x="186"/>
+        <item x="65"/>
+        <item x="218"/>
+        <item x="368"/>
+        <item x="315"/>
+        <item x="288"/>
+        <item x="83"/>
+        <item x="190"/>
+        <item x="360"/>
+        <item x="187"/>
+        <item x="81"/>
+        <item x="214"/>
+        <item x="233"/>
+        <item x="86"/>
+        <item x="129"/>
+        <item x="185"/>
+        <item x="188"/>
+        <item x="56"/>
+        <item x="210"/>
+        <item x="213"/>
+        <item x="297"/>
+        <item x="53"/>
+        <item x="76"/>
+        <item x="54"/>
+        <item x="46"/>
+        <item x="208"/>
+        <item x="44"/>
+        <item x="101"/>
+        <item x="3"/>
+        <item x="243"/>
+        <item x="334"/>
+        <item x="5"/>
+        <item x="112"/>
+        <item x="319"/>
+        <item x="195"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="183"/>
+        <item x="199"/>
+        <item x="301"/>
+        <item x="126"/>
+        <item x="28"/>
+        <item x="299"/>
+        <item x="205"/>
+        <item x="290"/>
+        <item x="314"/>
+        <item x="144"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="22"/>
+        <item x="158"/>
+        <item x="323"/>
+        <item x="348"/>
+        <item x="244"/>
+        <item x="324"/>
+        <item x="118"/>
+        <item x="232"/>
+        <item x="363"/>
+        <item x="149"/>
+        <item x="254"/>
+        <item x="234"/>
+        <item x="196"/>
+        <item x="372"/>
+        <item x="304"/>
+        <item x="73"/>
+        <item x="341"/>
+        <item x="262"/>
+        <item x="224"/>
+        <item x="105"/>
+        <item x="269"/>
+        <item x="113"/>
+        <item x="121"/>
+        <item x="125"/>
+        <item x="58"/>
+        <item x="123"/>
+        <item x="162"/>
+        <item x="24"/>
+        <item x="259"/>
+        <item x="165"/>
+        <item x="326"/>
+        <item x="145"/>
+        <item x="264"/>
+        <item x="307"/>
+        <item x="200"/>
+        <item x="146"/>
+        <item x="29"/>
+        <item x="182"/>
+        <item x="202"/>
+        <item x="92"/>
+        <item x="104"/>
+        <item x="238"/>
+        <item x="354"/>
+        <item x="281"/>
+        <item x="270"/>
+        <item x="356"/>
+        <item x="70"/>
+        <item x="337"/>
+        <item x="249"/>
+        <item x="50"/>
+        <item x="357"/>
+        <item x="344"/>
+        <item x="43"/>
+        <item x="68"/>
+        <item x="318"/>
+        <item x="349"/>
+        <item x="340"/>
+        <item x="266"/>
+        <item x="62"/>
+        <item x="284"/>
+        <item x="79"/>
+        <item x="75"/>
+        <item x="88"/>
+        <item x="60"/>
+        <item x="41"/>
+        <item x="308"/>
+        <item x="166"/>
+        <item x="133"/>
+        <item x="192"/>
+        <item x="351"/>
+        <item x="229"/>
+        <item x="194"/>
+        <item x="42"/>
+        <item x="141"/>
+        <item x="90"/>
+        <item x="140"/>
+        <item x="97"/>
+        <item x="342"/>
+        <item x="128"/>
+        <item x="4"/>
+        <item x="139"/>
+        <item x="143"/>
+        <item x="345"/>
+        <item x="51"/>
+        <item x="137"/>
+        <item x="23"/>
+        <item x="370"/>
+        <item x="173"/>
+        <item x="8"/>
+        <item x="150"/>
+        <item x="0"/>
+        <item x="250"/>
+        <item x="18"/>
+        <item x="347"/>
+        <item x="327"/>
+        <item x="191"/>
+        <item x="13"/>
+        <item x="49"/>
+        <item x="85"/>
+        <item x="164"/>
+        <item x="66"/>
+        <item x="316"/>
+        <item x="10"/>
+        <item x="252"/>
+        <item x="102"/>
+        <item x="246"/>
+        <item x="322"/>
+        <item x="155"/>
+        <item x="222"/>
+        <item x="279"/>
+        <item x="241"/>
+        <item x="64"/>
+        <item x="69"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de cliente" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1618,8 +6532,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312C4CA2-A45D-4086-AD3F-264DFD1ACBAE}">
+  <dimension ref="A3:B17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="11">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B17" s="11">
+        <v>390</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:I374"/>
+  <dimension ref="A1:I391"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -8337,16 +13385,16 @@
       <c r="A323" t="s">
         <v>345</v>
       </c>
-      <c r="B323" s="7" t="s">
+      <c r="B323" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C323" s="7" t="s">
+      <c r="C323" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D323" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E323" s="8" t="s">
+      <c r="E323" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H323">
@@ -8360,16 +13408,16 @@
       <c r="A324" t="s">
         <v>346</v>
       </c>
-      <c r="B324" s="7" t="s">
+      <c r="B324" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C324" s="7" t="s">
+      <c r="C324" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E324" s="8" t="s">
+      <c r="E324" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H324">
@@ -8383,16 +13431,16 @@
       <c r="A325" t="s">
         <v>347</v>
       </c>
-      <c r="B325" s="7" t="s">
+      <c r="B325" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C325" s="7" t="s">
+      <c r="C325" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D325" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E325" s="8" t="s">
+      <c r="E325" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H325">
@@ -8406,16 +13454,16 @@
       <c r="A326" t="s">
         <v>348</v>
       </c>
-      <c r="B326" s="7" t="s">
+      <c r="B326" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C326" s="7" t="s">
+      <c r="C326" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D326" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E326" s="8" t="s">
+      <c r="E326" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H326">
@@ -8429,16 +13477,16 @@
       <c r="A327" t="s">
         <v>349</v>
       </c>
-      <c r="B327" s="7" t="s">
+      <c r="B327" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C327" s="7" t="s">
+      <c r="C327" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E327" s="8" t="s">
+      <c r="E327" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H327">
@@ -8452,16 +13500,16 @@
       <c r="A328" t="s">
         <v>350</v>
       </c>
-      <c r="B328" s="7" t="s">
+      <c r="B328" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C328" s="7" t="s">
+      <c r="C328" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E328" s="8" t="s">
+      <c r="E328" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H328">
@@ -8475,16 +13523,16 @@
       <c r="A329" t="s">
         <v>351</v>
       </c>
-      <c r="B329" s="7" t="s">
+      <c r="B329" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C329" s="7" t="s">
+      <c r="C329" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E329" s="8" t="s">
+      <c r="E329" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H329">
@@ -8498,16 +13546,16 @@
       <c r="A330" t="s">
         <v>352</v>
       </c>
-      <c r="B330" s="7" t="s">
+      <c r="B330" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C330" s="7" t="s">
+      <c r="C330" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E330" s="8" t="s">
+      <c r="E330" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H330">
@@ -8521,16 +13569,16 @@
       <c r="A331" t="s">
         <v>353</v>
       </c>
-      <c r="B331" s="7" t="s">
+      <c r="B331" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C331" s="7" t="s">
+      <c r="C331" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E331" s="8" t="s">
+      <c r="E331" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H331">
@@ -8544,16 +13592,16 @@
       <c r="A332" t="s">
         <v>354</v>
       </c>
-      <c r="B332" s="7" t="s">
+      <c r="B332" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C332" s="7" t="s">
+      <c r="C332" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D332" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E332" s="8" t="s">
+      <c r="E332" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H332">
@@ -8567,16 +13615,16 @@
       <c r="A333" t="s">
         <v>355</v>
       </c>
-      <c r="B333" s="7" t="s">
+      <c r="B333" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C333" s="7" t="s">
+      <c r="C333" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D333" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E333" s="8" t="s">
+      <c r="E333" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H333">
@@ -8590,16 +13638,16 @@
       <c r="A334" t="s">
         <v>356</v>
       </c>
-      <c r="B334" s="7" t="s">
+      <c r="B334" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C334" s="7" t="s">
+      <c r="C334" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D334" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E334" s="8" t="s">
+      <c r="E334" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H334">
@@ -8613,16 +13661,16 @@
       <c r="A335" t="s">
         <v>357</v>
       </c>
-      <c r="B335" s="7" t="s">
+      <c r="B335" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C335" s="7" t="s">
+      <c r="C335" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E335" s="8" t="s">
+      <c r="E335" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H335">
@@ -8636,16 +13684,16 @@
       <c r="A336" t="s">
         <v>358</v>
       </c>
-      <c r="B336" s="7" t="s">
+      <c r="B336" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C336" s="7" t="s">
+      <c r="C336" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D336" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E336" s="8" t="s">
+      <c r="E336" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H336">
@@ -8659,16 +13707,16 @@
       <c r="A337" t="s">
         <v>359</v>
       </c>
-      <c r="B337" s="7" t="s">
+      <c r="B337" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C337" s="7" t="s">
+      <c r="C337" s="5" t="s">
         <v>360</v>
       </c>
       <c r="D337" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E337" s="8" t="s">
+      <c r="E337" s="6" t="s">
         <v>84</v>
       </c>
       <c r="H337">
@@ -8682,16 +13730,16 @@
       <c r="A338" t="s">
         <v>361</v>
       </c>
-      <c r="B338" s="7" t="s">
+      <c r="B338" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C338" s="7" t="s">
+      <c r="C338" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E338" s="8" t="s">
+      <c r="E338" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H338">
@@ -8705,16 +13753,16 @@
       <c r="A339" t="s">
         <v>111</v>
       </c>
-      <c r="B339" s="7" t="s">
+      <c r="B339" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C339" s="7" t="s">
+      <c r="C339" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D339" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E339" s="8" t="s">
+      <c r="E339" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H339">
@@ -8728,16 +13776,16 @@
       <c r="A340" t="s">
         <v>110</v>
       </c>
-      <c r="B340" s="7" t="s">
+      <c r="B340" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C340" s="7" t="s">
+      <c r="C340" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D340" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E340" s="8" t="s">
+      <c r="E340" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H340">
@@ -8751,16 +13799,16 @@
       <c r="A341" t="s">
         <v>109</v>
       </c>
-      <c r="B341" s="7" t="s">
+      <c r="B341" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C341" s="7" t="s">
+      <c r="C341" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D341" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E341" s="8" t="s">
+      <c r="E341" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H341">
@@ -8774,16 +13822,16 @@
       <c r="A342" t="s">
         <v>362</v>
       </c>
-      <c r="B342" s="7" t="s">
+      <c r="B342" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C342" s="7" t="s">
+      <c r="C342" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D342" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E342" s="8" t="s">
+      <c r="E342" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H342">
@@ -8797,16 +13845,16 @@
       <c r="A343" t="s">
         <v>363</v>
       </c>
-      <c r="B343" s="7" t="s">
+      <c r="B343" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C343" s="7" t="s">
+      <c r="C343" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D343" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E343" s="8" t="s">
+      <c r="E343" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H343">
@@ -8820,16 +13868,16 @@
       <c r="A344" t="s">
         <v>106</v>
       </c>
-      <c r="B344" s="7" t="s">
+      <c r="B344" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C344" s="7" t="s">
+      <c r="C344" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E344" s="8" t="s">
+      <c r="E344" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H344">
@@ -8843,16 +13891,16 @@
       <c r="A345" t="s">
         <v>105</v>
       </c>
-      <c r="B345" s="7" t="s">
+      <c r="B345" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C345" s="7" t="s">
+      <c r="C345" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D345" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E345" s="8" t="s">
+      <c r="E345" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H345">
@@ -8866,16 +13914,16 @@
       <c r="A346" t="s">
         <v>364</v>
       </c>
-      <c r="B346" s="7" t="s">
+      <c r="B346" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C346" s="7" t="s">
+      <c r="C346" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E346" s="8" t="s">
+      <c r="E346" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H346">
@@ -8889,16 +13937,16 @@
       <c r="A347" t="s">
         <v>365</v>
       </c>
-      <c r="B347" s="7" t="s">
+      <c r="B347" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C347" s="7" t="s">
+      <c r="C347" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E347" s="8" t="s">
+      <c r="E347" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H347">
@@ -8912,16 +13960,16 @@
       <c r="A348" t="s">
         <v>366</v>
       </c>
-      <c r="B348" s="7" t="s">
+      <c r="B348" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C348" s="7" t="s">
+      <c r="C348" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E348" s="8" t="s">
+      <c r="E348" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H348">
@@ -8935,16 +13983,16 @@
       <c r="A349" t="s">
         <v>367</v>
       </c>
-      <c r="B349" s="7" t="s">
+      <c r="B349" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C349" s="7" t="s">
+      <c r="C349" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D349" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E349" s="8" t="s">
+      <c r="E349" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H349">
@@ -8958,16 +14006,16 @@
       <c r="A350" t="s">
         <v>201</v>
       </c>
-      <c r="B350" s="7" t="s">
+      <c r="B350" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C350" s="7" t="s">
+      <c r="C350" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D350" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E350" s="8" t="s">
+      <c r="E350" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H350">
@@ -8981,16 +14029,16 @@
       <c r="A351" t="s">
         <v>368</v>
       </c>
-      <c r="B351" s="7" t="s">
+      <c r="B351" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C351" s="7" t="s">
+      <c r="C351" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E351" s="8" t="s">
+      <c r="E351" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H351">
@@ -9004,16 +14052,16 @@
       <c r="A352" t="s">
         <v>369</v>
       </c>
-      <c r="B352" s="7" t="s">
+      <c r="B352" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C352" s="7" t="s">
+      <c r="C352" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D352" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E352" s="8" t="s">
+      <c r="E352" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H352">
@@ -9027,16 +14075,16 @@
       <c r="A353" t="s">
         <v>370</v>
       </c>
-      <c r="B353" s="7" t="s">
+      <c r="B353" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C353" s="7" t="s">
+      <c r="C353" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E353" s="8" t="s">
+      <c r="E353" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H353">
@@ -9050,16 +14098,16 @@
       <c r="A354" t="s">
         <v>371</v>
       </c>
-      <c r="B354" s="7" t="s">
+      <c r="B354" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C354" s="7" t="s">
+      <c r="C354" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D354" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E354" s="8" t="s">
+      <c r="E354" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H354">
@@ -9073,16 +14121,16 @@
       <c r="A355" t="s">
         <v>372</v>
       </c>
-      <c r="B355" s="7" t="s">
+      <c r="B355" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C355" s="7" t="s">
+      <c r="C355" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D355" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E355" s="8" t="s">
+      <c r="E355" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H355">
@@ -9096,16 +14144,16 @@
       <c r="A356" t="s">
         <v>373</v>
       </c>
-      <c r="B356" s="7" t="s">
+      <c r="B356" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C356" s="7" t="s">
+      <c r="C356" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E356" s="8" t="s">
+      <c r="E356" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H356">
@@ -9119,16 +14167,16 @@
       <c r="A357" t="s">
         <v>374</v>
       </c>
-      <c r="B357" s="7" t="s">
+      <c r="B357" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C357" s="7" t="s">
+      <c r="C357" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D357" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E357" s="8" t="s">
+      <c r="E357" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H357">
@@ -9142,16 +14190,16 @@
       <c r="A358" t="s">
         <v>375</v>
       </c>
-      <c r="B358" s="7" t="s">
+      <c r="B358" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C358" s="7" t="s">
+      <c r="C358" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D358" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E358" s="8" t="s">
+      <c r="E358" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H358">
@@ -9165,16 +14213,16 @@
       <c r="A359" t="s">
         <v>376</v>
       </c>
-      <c r="B359" s="7" t="s">
+      <c r="B359" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C359" s="7" t="s">
+      <c r="C359" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E359" s="8" t="s">
+      <c r="E359" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H359">
@@ -9188,16 +14236,16 @@
       <c r="A360" t="s">
         <v>377</v>
       </c>
-      <c r="B360" s="7" t="s">
+      <c r="B360" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C360" s="7" t="s">
+      <c r="C360" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E360" s="8" t="s">
+      <c r="E360" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H360">
@@ -9211,16 +14259,16 @@
       <c r="A361" t="s">
         <v>378</v>
       </c>
-      <c r="B361" s="7" t="s">
+      <c r="B361" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C361" s="7" t="s">
+      <c r="C361" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E361" s="8" t="s">
+      <c r="E361" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H361">
@@ -9234,16 +14282,16 @@
       <c r="A362" t="s">
         <v>379</v>
       </c>
-      <c r="B362" s="7" t="s">
+      <c r="B362" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C362" s="7" t="s">
+      <c r="C362" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E362" s="8" t="s">
+      <c r="E362" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H362">
@@ -9257,16 +14305,16 @@
       <c r="A363" t="s">
         <v>380</v>
       </c>
-      <c r="B363" s="7" t="s">
+      <c r="B363" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C363" s="7" t="s">
+      <c r="C363" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E363" s="8" t="s">
+      <c r="E363" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H363">
@@ -9280,16 +14328,16 @@
       <c r="A364" t="s">
         <v>381</v>
       </c>
-      <c r="B364" s="7" t="s">
+      <c r="B364" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C364" s="7" t="s">
+      <c r="C364" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D364" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E364" s="8" t="s">
+      <c r="E364" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H364">
@@ -9303,16 +14351,16 @@
       <c r="A365" t="s">
         <v>382</v>
       </c>
-      <c r="B365" s="7" t="s">
+      <c r="B365" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C365" s="7" t="s">
+      <c r="C365" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D365" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E365" s="8" t="s">
+      <c r="E365" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H365">
@@ -9326,16 +14374,16 @@
       <c r="A366" t="s">
         <v>383</v>
       </c>
-      <c r="B366" s="7" t="s">
+      <c r="B366" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C366" s="7" t="s">
+      <c r="C366" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E366" s="8" t="s">
+      <c r="E366" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H366">
@@ -9349,16 +14397,16 @@
       <c r="A367" t="s">
         <v>384</v>
       </c>
-      <c r="B367" s="7" t="s">
+      <c r="B367" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C367" s="7" t="s">
+      <c r="C367" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D367" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E367" s="8" t="s">
+      <c r="E367" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H367">
@@ -9372,16 +14420,16 @@
       <c r="A368" t="s">
         <v>385</v>
       </c>
-      <c r="B368" s="7" t="s">
+      <c r="B368" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C368" s="7" t="s">
+      <c r="C368" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D368" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E368" s="8" t="s">
+      <c r="E368" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H368">
@@ -9395,16 +14443,16 @@
       <c r="A369" t="s">
         <v>386</v>
       </c>
-      <c r="B369" s="7" t="s">
+      <c r="B369" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C369" s="7" t="s">
+      <c r="C369" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D369" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E369" s="8" t="s">
+      <c r="E369" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H369">
@@ -9418,16 +14466,16 @@
       <c r="A370" t="s">
         <v>387</v>
       </c>
-      <c r="B370" s="7" t="s">
+      <c r="B370" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C370" s="7" t="s">
+      <c r="C370" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D370" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E370" s="8" t="s">
+      <c r="E370" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H370">
@@ -9441,16 +14489,16 @@
       <c r="A371" t="s">
         <v>388</v>
       </c>
-      <c r="B371" s="7" t="s">
+      <c r="B371" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C371" s="7" t="s">
+      <c r="C371" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D371" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E371" s="8" t="s">
+      <c r="E371" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H371">
@@ -9464,16 +14512,16 @@
       <c r="A372" t="s">
         <v>389</v>
       </c>
-      <c r="B372" s="7" t="s">
+      <c r="B372" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C372" s="7" t="s">
+      <c r="C372" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D372" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E372" s="8" t="s">
+      <c r="E372" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H372">
@@ -9487,16 +14535,16 @@
       <c r="A373" t="s">
         <v>390</v>
       </c>
-      <c r="B373" s="7" t="s">
+      <c r="B373" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C373" s="7" t="s">
+      <c r="C373" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D373" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E373" s="8" t="s">
+      <c r="E373" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H373">
@@ -9510,16 +14558,16 @@
       <c r="A374" t="s">
         <v>391</v>
       </c>
-      <c r="B374" s="7" t="s">
+      <c r="B374" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C374" s="7" t="s">
+      <c r="C374" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E374" s="8" t="s">
+      <c r="E374" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H374">
@@ -9529,8 +14577,396 @@
         <v>371</v>
       </c>
     </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>392</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C375" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D375" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E375" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H375">
+        <v>8</v>
+      </c>
+      <c r="I375">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>393</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C376" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D376" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E376" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H376">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>394</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C377" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D377" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E377" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H377">
+        <v>8</v>
+      </c>
+      <c r="I377">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>395</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C378" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D378" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E378" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H378">
+        <v>8</v>
+      </c>
+      <c r="I378">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>396</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D379" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E379" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H379">
+        <v>8</v>
+      </c>
+      <c r="I379">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>397</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E380" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H380">
+        <v>8</v>
+      </c>
+      <c r="I380">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>398</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C381" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D381" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E381" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H381">
+        <v>8</v>
+      </c>
+      <c r="I381">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>399</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D382" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E382" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H382">
+        <v>8</v>
+      </c>
+      <c r="I382">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>400</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C383" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D383" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E383" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H383">
+        <v>8</v>
+      </c>
+      <c r="I383">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>401</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C384" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E384" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H384">
+        <v>8</v>
+      </c>
+      <c r="I384">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>402</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C385" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D385" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E385" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H385">
+        <v>8</v>
+      </c>
+      <c r="I385">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>403</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C386" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D386" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E386" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H386">
+        <v>8</v>
+      </c>
+      <c r="I386">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>404</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C387" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D387" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E387" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H387">
+        <v>8</v>
+      </c>
+      <c r="I387">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>405</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C388" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E388" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H388">
+        <v>8</v>
+      </c>
+      <c r="I388">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>406</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C389" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E389" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H389">
+        <v>8</v>
+      </c>
+      <c r="I389">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>407</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E390" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H390">
+        <v>8</v>
+      </c>
+      <c r="I390">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>408</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C391" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D391" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E391" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H391">
+        <v>8</v>
+      </c>
+      <c r="I391">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H275" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}"/>
+  <autoFilter ref="A1:H374" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H78">
     <sortCondition ref="E2:E78"/>
   </sortState>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,21 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA437F6-DB7D-47A9-ACCE-2C388DECDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD794356-7964-4115-AE12-5C227C19C9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="1" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$H$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="409">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -1259,15 +1255,6 @@
   </si>
   <si>
     <t>andreza dias gomes</t>
-  </si>
-  <si>
-    <t>Rótulos de Linha</t>
-  </si>
-  <si>
-    <t>Total Geral</t>
-  </si>
-  <si>
-    <t>Contagem de cliente</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1369,11 +1356,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1389,4851 +1371,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Suporte" refreshedDate="46296.588252430556" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="390" xr:uid="{87FE605C-F668-458F-8EBE-B9812B8C88B2}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H391" sheet="Planilha1"/>
-  </cacheSource>
-  <cacheFields count="8">
-    <cacheField name="cliente" numFmtId="0">
-      <sharedItems count="377">
-        <s v="Tatiane Moraes dos Santos "/>
-        <s v="Margarida Moraes do nascimento "/>
-        <s v="Maria Antônia Ramos Da Silva "/>
-        <s v="Marciane Moraes dos Santos de Sousa "/>
-        <s v="Sofia Moraes dos Santos "/>
-        <s v="Marcinete Moraes dos Santos "/>
-        <s v="José Maria Moraes dos Santos "/>
-        <s v="Domingos Moraes dos Santos"/>
-        <s v="tamires kevelim barros dos santos"/>
-        <s v="edivania conceição da silva"/>
-        <s v="vitoria conceição da silva"/>
-        <s v="irionilson rodrigues da silva"/>
-        <s v="guilherme linho da silva"/>
-        <s v="tryla barros sobrinho"/>
-        <s v="carlos henrik da silva britto"/>
-        <s v="edivan conceição da silva"/>
-        <s v="adrielly silva da silva"/>
-        <s v="arlete ramos da silva"/>
-        <s v="thainara ramos picanço"/>
-        <s v="alcivane barros da silva"/>
-        <s v="aurea carvalho de almeida "/>
-        <s v="katryny silva da silva"/>
-        <s v="maria jos[é de almeida"/>
-        <s v="taiana palheta de souza"/>
-        <s v="odielton as silva ramos"/>
-        <s v="ana clara do espirito santo"/>
-        <s v="edemar coutinho ramos"/>
-        <s v="bianca borges de oliveira "/>
-        <s v="maria de fatima ramos picanço"/>
-        <s v="paulo guilherme coutinho da silva"/>
-        <s v="antonio Santana lopes"/>
-        <s v="ana maria da silva"/>
-        <s v="darlison Santana"/>
-        <s v="camila rodrigues"/>
-        <s v="david Santana"/>
-        <s v="dhyefferson farias"/>
-        <s v="iracildo willias faria"/>
-        <s v="filipe farias"/>
-        <s v="ediene farias"/>
-        <s v="francimar penha"/>
-        <s v="françuar tolosa"/>
-        <s v="rosilene dos santos"/>
-        <s v="selena farias"/>
-        <s v="rene mendes"/>
-        <s v="marcelo rodrigues"/>
-        <s v="celita dos santos"/>
-        <s v="manoel francisco costa"/>
-        <s v="dorenilson de oliveira"/>
-        <s v="josiane dos santos"/>
-        <s v="valdirene conceição dos santos"/>
-        <s v="rangele vitoria pereira nascimento"/>
-        <s v="susan de azevedo gomes"/>
-        <s v="josivan campos correa"/>
-        <s v="maiara costa souza"/>
-        <s v="mailom campos"/>
-        <s v="idionete tavares de souza"/>
-        <s v="luian souza campos"/>
-        <s v="josue souza mourão"/>
-        <s v="nerivaldo maciel dos santos"/>
-        <s v="elusley rezende campos"/>
-        <s v="rosilene amaral resende"/>
-        <s v="eldclei penha campos"/>
-        <s v="ronaldo penha campos"/>
-        <s v="cristiano da costa campos"/>
-        <s v="ziany de souza santos"/>
-        <s v="lenilton barbosa santos "/>
-        <s v="veldeny oliveira passos"/>
-        <s v="caroline amaral rezende"/>
-        <s v="resenalda barbosa dos santos"/>
-        <s v="zineide dos santos campos"/>
-        <s v="raimundo babosa dos santos"/>
-        <s v="leidieli campos amaral"/>
-        <s v="cristiane penha campos"/>
-        <s v="michel jesus miranda"/>
-        <s v="ledina maciel penha"/>
-        <s v="rosiely maciel campos"/>
-        <s v="maicom maicel campos"/>
-        <s v="eldilei penha campos"/>
-        <s v="cardine amaral resende"/>
-        <s v="rosenalda barbosa dos santos"/>
-        <s v="elvisley resende campos"/>
-        <s v="luan souza campos"/>
-        <s v="eliana costa souza"/>
-        <s v="leucimar maciel pires"/>
-        <s v="ilson tavares souza"/>
-        <s v="vanuza amaral penha"/>
-        <s v="luciane penha souza"/>
-        <s v="josimar pires dos santos"/>
-        <s v="rosilena amaral resende"/>
-        <s v="genival quaresma dos santos"/>
-        <s v="sheila passos amaral"/>
-        <s v="Iranilson da Silva de Souza "/>
-        <s v="Pedro Paulo dos Santos Tavares "/>
-        <s v="Civaldo Pacheco Barbosa "/>
-        <s v="Emílio Pablo costa Tolosa "/>
-        <s v="Fabrício Tolosa Ramos "/>
-        <s v="Jose Rodolfo Dos Santos Tavares"/>
-        <s v="Silviane Tolosa Ramos"/>
-        <s v="Dougla Silva Cardoso"/>
-        <s v="Guilherme Costa Tolosa"/>
-        <s v="GLENDA FRANKLIN CRUZ"/>
-        <s v="Marciane Moraes dos Santos de Sousa"/>
-        <s v="Wellington Lemos nunis "/>
-        <s v="klever luan ferreira Gomes"/>
-        <s v="pétala Ariele Nunes modesto "/>
-        <s v="Nádia Pereira Nunes "/>
-        <s v="Ana melqlen de Souza do Carmo "/>
-        <s v="Adria taila Nunes modesto "/>
-        <s v="Adielton Pereira Nunes "/>
-        <s v="jhessica shirley de Oliveira Silva"/>
-        <s v="Jhennefer shenon de Oliveira Silva"/>
-        <s v="Ágatha jasminy de Oliveira Lima"/>
-        <s v="Márcio Gabriel dos santos ferreira"/>
-        <s v="Nayane Pereira Nunes "/>
-        <s v="Ana Cristina Gama Rodrigues"/>
-        <s v="Eriton Martins pereira"/>
-        <s v="Gleice Kelly Pereira Nunes "/>
-        <s v="Adielson Pereira Nunes"/>
-        <s v="Maria Zenália Ribeiro da Silva "/>
-        <s v="Aldiene Pereira Nunes"/>
-        <s v="Eduardo da Silva Azevedo "/>
-        <s v="Nayara Pereira Nunes"/>
-        <s v="Edson Gomes de Oliveira"/>
-        <s v="Neuraci pereira magno"/>
-        <s v="Lana Furtado"/>
-        <s v="Neikson Nicolau"/>
-        <s v="Maria da Penha"/>
-        <s v="Fabiana da Conceição Araújo "/>
-        <s v="Sinaria Regina Costa"/>
-        <s v="Luciane Souza de Oliveira "/>
-        <s v="Cloudiovan Pinheiro Amaral"/>
-        <s v="Francione Serrão Freitas "/>
-        <s v="Celiomar da Luz Silva "/>
-        <s v="Ruane Larissa da Trindade Ramos"/>
-        <s v="Ingrid Santos da Silva "/>
-        <s v="João Cleiton Luz Da Silva "/>
-        <s v="Iasmim da Luz Silva "/>
-        <s v="Suzana Dalvis "/>
-        <s v="Juciano luz da Silva "/>
-        <s v="Suane da Luz silva "/>
-        <s v="Sibelli Luz Da Silva "/>
-        <s v="Sérgio da Luz Silva "/>
-        <s v="James Feber de Oliveira Júnior "/>
-        <s v="Suelen  Luz  da Silva"/>
-        <s v="MARIA DO SOCORRO TEIXEIRA SILVA"/>
-        <s v="OSVALDO QUEIROZ DA SILVA"/>
-        <s v="PAULO ENUS TEIXEIRA SILVA"/>
-        <s v="AYENN TEIXEIRA SILVA"/>
-        <s v="FERNANDA MONTEIRO DA SILVA"/>
-        <s v="MARLUCIA QUEIROZ TEIXEIRA"/>
-        <s v="Tamires Kevelim Barros dos Santos "/>
-        <s v="Josimar Silva da Silva"/>
-        <s v="Beatriz Vitória Souza dos Santos "/>
-        <s v="Dulcineia Santos da Silva "/>
-        <s v="Elizia Maria R. Lopes de Souza"/>
-        <s v="Yasmim Silva dos Santos "/>
-        <s v="Dione Moraes dos Santos "/>
-        <s v="Enzo Henrique muniz de Castro "/>
-        <s v="Maria Lenilda Silva dos Santos "/>
-        <s v="maria iracema da silva "/>
-        <s v="maria iraci da silva"/>
-        <s v="joão da silva costa"/>
-        <s v="ocinete pereira da silva"/>
-        <s v="juliana pires da silva"/>
-        <s v="vaulucio da silva "/>
-        <s v="osmandina da silva"/>
-        <s v="ruan pires da silva "/>
-        <s v="aline santos da silva "/>
-        <s v="eliana palmerim costa"/>
-        <s v="doriana da silva nunes"/>
-        <s v="itelimira da silva "/>
-        <s v="ana claudia da silva de jesus"/>
-        <s v="josimar silva da silva "/>
-        <s v="tamires kevelem barros dos sanots"/>
-        <s v="joelma padilha ferreria"/>
-        <s v="João Barbosa Tolosa "/>
-        <s v="Alanna Ani Leal Dos Santos Silva"/>
-        <s v="KAUE COSTA DE ALMEIDA"/>
-        <s v="ANDRESSA RAYANA MACIEL PINHEIRO"/>
-        <s v="ANDREIA MACIEL DOS SANTOS"/>
-        <s v="JORGE SANTOS DE LIMA"/>
-        <s v="KAROLINE LOPES OLIVEIRA"/>
-        <s v="PEDRO PATRICJ MORAES QUINTELA"/>
-        <s v="MARIA CAIDETE MELO"/>
-        <s v="FRANCIELE MELO SALES"/>
-        <s v="LUCICLEIA ROCHA DOS SANTOS REIS "/>
-        <s v="LEILARA FERREIRA DOS REIS"/>
-        <s v="LISBELA ISABEL DOS REIS "/>
-        <s v="LUCILENE ROCHA DOS SANTOS"/>
-        <s v="JPÃO VIANA DE LIMA"/>
-        <s v="LIDIANE CORDEIRO PENA"/>
-        <s v="THYAGO RYAN PENA FARIAS"/>
-        <s v="SABRINA CAMPOS CRUZ"/>
-        <s v="FELIPE SILVA  DOS SANTOS "/>
-        <s v="SANDRA DOS SANTOS DA SILVA "/>
-        <s v="MARCOS MATEUS DOS SANTOS"/>
-        <s v="Mayara Fernandes da Silva"/>
-        <s v="Flávio Rafael Santana Neves"/>
-        <s v="Jeremias Santos Rodrigues "/>
-        <s v="Maria Claudete Rocha Melo"/>
-        <s v="Paula Tavares de Oliveira "/>
-        <s v="Brayan Davi Quintela da Silva "/>
-        <s v="Pedro Patrick Moraes Quintela "/>
-        <s v="Cleyse Derielle Melo Quintela "/>
-        <s v="Edrio Riquellme Quintela Chermont"/>
-        <s v="Maria de Nazaré de Freitas Garcia"/>
-        <s v="Edna de Jesus dos Santos "/>
-        <s v="Keila da Silva Freitas "/>
-        <s v="Manoel Raimundo Alves Barbosa "/>
-        <s v="Erondina Miranda Cortes "/>
-        <s v="Luiz Claudio miranda dos santos"/>
-        <s v="Caio Luygui Amoras"/>
-        <s v="Brenda Farias da Silva"/>
-        <s v="Luiz Kaue Monteiro Barbosa "/>
-        <s v="Luane Christiane Costa Gonçalves "/>
-        <s v="Flávia Camily Cordeiro da Silva"/>
-        <s v="Ana Paula Figueiredo Corrêia "/>
-        <s v="João Gustavo da Silva de Deus "/>
-        <s v="Leonardo Henrique Rodrigues "/>
-        <s v="Ana Carolina Pereira Pantoja "/>
-        <s v="Breno Santana da Silva "/>
-        <s v="Ezequiel Marques da Silva"/>
-        <s v="Yasmin Brandão da Silva "/>
-        <s v="Ellen Cristina Ferreira dos Santos "/>
-        <s v="Moacir Gomes Santos dos Santos "/>
-        <s v="Erika Adriana Cardoso de Souza Barreto"/>
-        <s v="José do Socorro Pena da Silva "/>
-        <s v="Alana Correia Soares "/>
-        <s v="Isabele da Silva Sampaio "/>
-        <s v="Samuel Sillas da Silva Chaves "/>
-        <s v="Benedito Souza dos Santos "/>
-        <s v="Geize de Oliveira Magno"/>
-        <s v="Marilena Mendes Monteiro "/>
-        <s v="Luanna Gyovanna Farias Gomes"/>
-        <s v="Mayane Da Luz de Oliveira"/>
-        <s v="Fabian Graziele Nogueira de Oliveira"/>
-        <s v="Juliana Farias Ramos"/>
-        <s v="Amanda Farias Gomes"/>
-        <s v="Peterson Cristian Moura e Silva"/>
-        <s v="Daniel Barros dos Santos"/>
-        <s v="Cristiana Raiça Piedade Modesto"/>
-        <s v="Ydla Aguiar Morais"/>
-        <s v="Karina Aguiar Morais"/>
-        <s v="Marcilene da Luz de Oliveira"/>
-        <s v="Maria Rosinete Lobato da Luz"/>
-        <s v="Carla Lidiane Quaresma Farias"/>
-        <s v="Wemesson Farias da Silva"/>
-        <s v="Antonio Jose Quaresma Filho"/>
-        <s v="Francisca Maria Quaresma Farias"/>
-        <s v="Ramon Farias Ramos"/>
-        <s v="Teresa Farias"/>
-        <s v="Laudelina Ferreira Aguiar"/>
-        <s v="Wane Cristina Silva Gama"/>
-        <s v="Karia Cristina Pinheiro Picanço"/>
-        <s v="Mateus de Souza Sales"/>
-        <s v="Kaio Cezar dos Santos Abreu"/>
-        <s v="Carlos Alberto Flexa Santos"/>
-        <s v="Erica de Oliveira Magno"/>
-        <s v="Francidalva de Melo Sales"/>
-        <s v="Omar Glauber de Melo Sales "/>
-        <s v="José Franciuei de Melo Sales "/>
-        <s v="Francineide de Melo Sales "/>
-        <s v="Mizael Aguiar Souza"/>
-        <s v="Francivalda de Melo Sales "/>
-        <s v="Otni Frank de Melo Silva"/>
-        <s v="Charles de Melo Batista"/>
-        <s v="Rodrigo Moura Gouveia"/>
-        <s v="Celma do socorro da Costa chagas"/>
-        <s v="Esteffany Raully chagas Duarte "/>
-        <s v="Nahely Nariel Tolosa Marques "/>
-        <s v="Raimunda Costa da Silva "/>
-        <s v="Heloiza Ferreira da Silva "/>
-        <s v="Gleice Helena Lopes Rodrigues "/>
-        <s v="Doriana da Silva Nunes "/>
-        <s v="Beatriz Magno Meireles "/>
-        <s v="Itelmira da Silva "/>
-        <s v="Adriana Silva Nascimento "/>
-        <s v="Emyla Raquel Rocha Pimentel "/>
-        <s v="Jorge Rodrigues Pereira "/>
-        <s v="Yasmin Ramilla Picanço da Costa "/>
-        <s v="Ediane Pantoja Almeida de Souza "/>
-        <s v="Railana Goes de Souza "/>
-        <s v="Jose Freitas Gonçalves "/>
-        <s v="Jositelma barreto soares de oliveira"/>
-        <s v="ronielson soares de oliviera"/>
-        <s v="francisco viana de oliveira"/>
-        <s v="geová magno de oliveira"/>
-        <s v="francisca pereira da silva"/>
-        <s v="leticia dos santos ribeiro"/>
-        <s v="francisco dos santos ribeiro"/>
-        <s v="maria diolena tenorio da silva"/>
-        <s v="jose cardoso da silva"/>
-        <s v="edenice dos santos pires"/>
-        <s v="alberto duarte soares"/>
-        <s v="erisson pablo gomes ribeiro"/>
-        <s v="ellen nayara gomes ribeiro"/>
-        <s v="denilson souza de souza"/>
-        <s v="luvas edielson costa pires"/>
-        <s v="elris barbosa ribeiro"/>
-        <s v="maria de lourdes da silva gomes"/>
-        <s v="franciane silva de souza"/>
-        <s v="maria cristina souza da silva"/>
-        <s v="jomar da silva tenorio"/>
-        <s v="alcione pereira de souza "/>
-        <s v="mayro souza tenenorio"/>
-        <s v="gleiciane da silva costa"/>
-        <s v="alexandre dias ribeiro"/>
-        <s v="patricia flexa pereira"/>
-        <s v="rosinei da silva texeira"/>
-        <s v="angela caroline cardoso silva"/>
-        <s v="cleuma da silva carodoso"/>
-        <s v="adomar da silva gomes"/>
-        <s v="lealdo alves da silva "/>
-        <s v="cleber da silva cardoso"/>
-        <s v="maria do socorro do nascimento"/>
-        <s v="leticia do nascimento barbosa"/>
-        <s v="verinaldo guedes de figueiredo"/>
-        <s v="hellana medeiros"/>
-        <s v="rita cassia souza dos santos"/>
-        <s v="marcio vagner feliz"/>
-        <s v="fabricio henrique douza dos santos"/>
-        <s v="josé geovane cristino"/>
-        <s v="yasmim da costa lima"/>
-        <s v="maria lucia gomes de souza "/>
-        <s v="maria sousa de almeida"/>
-        <s v="jose raimundo balieiro dos reis"/>
-        <s v="osvaldo almeida de lima"/>
-        <s v="thatiane da silva nobre"/>
-        <s v="ilete souza de belieiro"/>
-        <s v="Guilherme Costa Tolosa "/>
-        <s v="Fabrício Tolosa Ramos"/>
-        <s v="Emílio Pablo costa Tolosa"/>
-        <s v="Iranilson da Silva de Souza"/>
-        <s v="Deonaldo Maciel Sarmento"/>
-        <s v="Marcilene Neves Pinheiro"/>
-        <s v="João Barbosa Tolosa"/>
-        <s v="Kauê Costa De Almeida "/>
-        <s v="Raione Almeida Pessoa "/>
-        <s v="Dayse Barbosa Dos Santos "/>
-        <s v="Ana Carolina Pantoja Nascimento "/>
-        <s v="Rodrigo dos Reis Nascimento "/>
-        <s v="Mirail Belém Da Silva "/>
-        <s v="Simone De Paula Brito "/>
-        <s v=" Flávia Ameliny Lobato Pantoja "/>
-        <s v="Regiane Alves Machado"/>
-        <s v="Suely Lobato Dos Santos "/>
-        <s v="Deibson Dos Reis Leite "/>
-        <s v="Thalia Santos Pantoja "/>
-        <s v="Maria Raimunda Dos Santos Costa "/>
-        <s v="Robelino Silva Tolosa "/>
-        <s v="Agatha Maly Lobato Pantoja"/>
-        <s v="Sabrina Nascimento"/>
-        <s v=" Lorran Junior Santos Nepomuceno"/>
-        <s v="Iraercio Tavares Do nascimento "/>
-        <s v="Rafaela Monteiro Dos Santos "/>
-        <s v="Antônio Amaral Vieira "/>
-        <s v="Raimunda Monteiro Dos Santos "/>
-        <s v="Ray Vieira Dos Santos "/>
-        <s v="Andriele vieira Dos Santos "/>
-        <s v="Gabriela Monteiro Dos Santos "/>
-        <s v="lilliana gomes cardim"/>
-        <s v="ana lucia silva gomes"/>
-        <s v="ednéia do nascimento jesus"/>
-        <s v="marinaldo de jesus ribeiro"/>
-        <s v="edmilson gomes silva"/>
-        <s v="dimayara anastacia pinto batista"/>
-        <s v="edwilson do carmo santana silva"/>
-        <s v="eziele nascimento pantoja"/>
-        <s v="leonardo lima gomes"/>
-        <s v="erika patricia correa silva"/>
-        <s v="tais gomes silva"/>
-        <s v="isabelle gomes silva"/>
-        <s v="mayara silva gomes"/>
-        <s v="enájla dos reis jonas duarte"/>
-        <s v="jamaira dos reia jonas duarte"/>
-        <s v="elicivaldo dos santos duarte"/>
-        <s v="andreza dias gomes"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Apontador" numFmtId="0">
-      <sharedItems count="13">
-        <s v="FERNANDO SANTOS"/>
-        <s v="ADRYELLY SILVA DA SILVA"/>
-        <s v="ANE TOLOSA"/>
-        <s v="GLENDA"/>
-        <s v="JOSIVAN"/>
-        <s v="EDSON"/>
-        <s v="Ayenn Teixeira Silva"/>
-        <s v="val"/>
-        <s v="RAY"/>
-        <s v="Mel"/>
-        <s v="Brenda"/>
-        <s v="Luanna"/>
-        <s v="Ilete"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name=" atendente" numFmtId="0">
-      <sharedItems count="14">
-        <s v="FERNANDO SANTOS"/>
-        <s v="ADRYELLY SILVA DA SILVA"/>
-        <s v="ANE TOLOSA"/>
-        <s v="GLENDA"/>
-        <s v="JOSIVAN"/>
-        <s v="EDSON "/>
-        <s v="Ayenn Teixeira Silva"/>
-        <s v="val"/>
-        <s v="RAY"/>
-        <s v="Mel"/>
-        <s v="Brenda"/>
-        <s v="Luanna"/>
-        <s v="EDSON"/>
-        <s v="Ilete"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Estado" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="municipio" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Comunidade" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="Localidade" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="zona" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="14"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="390">
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="13"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="14"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="15"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="17"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="18"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="19"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="21"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="23"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="24"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="25"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="26"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="28"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="29"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="30"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="31"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="32"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="33"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="35"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="36"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="37"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="39"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="40"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="41"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="42"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="43"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="44"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="45"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="46"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="48"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="49"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="50"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="51"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="52"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="53"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="54"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="55"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="56"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="57"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="58"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="59"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="60"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="61"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="62"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="63"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="64"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="65"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="66"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="67"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="68"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="69"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="70"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="71"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="72"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="73"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="74"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="75"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="76"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="77"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="78"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="79"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="80"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="81"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="82"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="83"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="84"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="85"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="86"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="87"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="88"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="89"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="90"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="91"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="92"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="94"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="95"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="96"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="97"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="98"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="99"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="100"/>
-    <x v="3"/>
-    <x v="3"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="101"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="102"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="103"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="104"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="105"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="106"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="107"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="108"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="109"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="110"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="111"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="112"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="113"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="114"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="115"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="116"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="117"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="118"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="119"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="120"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="121"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="122"/>
-    <x v="5"/>
-    <x v="5"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="123"/>
-    <x v="5"/>
-    <x v="5"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="124"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="125"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="126"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="127"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="128"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="129"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="130"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="131"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="132"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="133"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="134"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="135"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="136"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="137"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="138"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="139"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="140"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="141"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="142"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="143"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="144"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="145"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="146"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="147"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="148"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="149"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="150"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="151"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="152"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="153"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="154"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="155"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="156"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="157"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="158"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="159"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="160"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="161"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="162"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="163"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="164"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="165"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="166"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="167"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="168"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="169"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="170"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="171"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="172"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="173"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="174"/>
-    <x v="7"/>
-    <x v="7"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="175"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="176"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="177"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="178"/>
-    <x v="8"/>
-    <x v="8"/>
-    <s v="Ap"/>
-    <s v="Amapá"/>
-    <m/>
-    <m/>
-    <n v="1"/>
-  </r>
-  <r>
-    <x v="179"/>
-    <x v="8"/>
-    <x v="8"/>
-    <s v="Ap"/>
-    <s v="Amapá"/>
-    <m/>
-    <m/>
-    <n v="1"/>
-  </r>
-  <r>
-    <x v="180"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="181"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="182"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="183"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="184"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="185"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="186"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="187"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="188"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="189"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="190"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="191"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="192"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="193"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="194"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="195"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="196"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="197"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="198"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="199"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="200"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="201"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="202"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="203"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="204"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="205"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="206"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="207"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="208"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="209"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="210"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="211"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="212"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="213"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="214"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="215"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="216"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="217"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="218"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="219"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="220"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="221"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="222"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="223"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="224"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="225"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="226"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="227"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="228"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="229"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="230"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="231"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="232"/>
-    <x v="10"/>
-    <x v="10"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="233"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="234"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="12"/>
-  </r>
-  <r>
-    <x v="235"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="236"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="237"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="238"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="239"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="240"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="241"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="242"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="243"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="12"/>
-  </r>
-  <r>
-    <x v="244"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="12"/>
-  </r>
-  <r>
-    <x v="245"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="246"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="247"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="248"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="249"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="250"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="251"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="252"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="253"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="254"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="1"/>
-  </r>
-  <r>
-    <x v="255"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="256"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="257"/>
-    <x v="11"/>
-    <x v="11"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="258"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="259"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="260"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="261"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="262"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="263"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="264"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="265"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="266"/>
-    <x v="9"/>
-    <x v="9"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="267"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="268"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="269"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="PORTO GRANDE"/>
-    <m/>
-    <m/>
-    <n v="12"/>
-  </r>
-  <r>
-    <x v="270"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="271"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="272"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="273"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="274"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="275"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Santana"/>
-    <m/>
-    <m/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="276"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="277"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="278"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="279"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="280"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="PORTO GRANDE"/>
-    <m/>
-    <m/>
-    <n v="11"/>
-  </r>
-  <r>
-    <x v="281"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="Mazagão"/>
-    <m/>
-    <m/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="282"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Ap"/>
-    <s v="PORTO GRANDE"/>
-    <m/>
-    <m/>
-    <n v="11"/>
-  </r>
-  <r>
-    <x v="283"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="284"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="285"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="286"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="287"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="288"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="289"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="290"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="291"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="292"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="293"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="294"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="295"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="296"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="297"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="298"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="299"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="300"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="301"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="302"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="303"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="304"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="305"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="306"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="307"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="308"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="309"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="310"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="311"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="312"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="313"/>
-    <x v="5"/>
-    <x v="12"/>
-    <s v="Ap"/>
-    <s v="Laranjal do jari"/>
-    <m/>
-    <m/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="314"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="315"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="316"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="317"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="318"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="319"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="320"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="321"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="322"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="323"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="324"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="325"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="326"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="327"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="328"/>
-    <x v="12"/>
-    <x v="13"/>
-    <s v="Ap"/>
-    <s v="Macapá"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="329"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="98"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="97"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="96"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="330"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="331"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="93"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="92"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="332"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="333"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="334"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="335"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="176"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="336"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="337"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="338"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="339"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="340"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="341"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="342"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="343"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="344"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="345"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="346"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="347"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="348"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="349"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="350"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="351"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="352"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="353"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="354"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="355"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="356"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="357"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="358"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="359"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Ap"/>
-    <s v="Itaubal"/>
-    <m/>
-    <m/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="360"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="361"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="362"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="363"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="364"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="365"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="366"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="367"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="368"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="369"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="370"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="371"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="372"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="373"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="374"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="375"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="376"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Ap"/>
-    <s v="Tartarugalzinho"/>
-    <m/>
-    <m/>
-    <n v="8"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8490535A-E6C1-4F41-9EDC-C324212FFB17}" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField dataField="1" showAll="0">
-      <items count="378">
-        <item x="343"/>
-        <item x="352"/>
-        <item x="117"/>
-        <item x="108"/>
-        <item x="311"/>
-        <item x="107"/>
-        <item x="276"/>
-        <item x="16"/>
-        <item x="111"/>
-        <item x="350"/>
-        <item x="227"/>
-        <item x="176"/>
-        <item x="293"/>
-        <item x="303"/>
-        <item x="19"/>
-        <item x="119"/>
-        <item x="306"/>
-        <item x="167"/>
-        <item x="237"/>
-        <item x="339"/>
-        <item x="219"/>
-        <item x="25"/>
-        <item x="171"/>
-        <item x="114"/>
-        <item x="361"/>
-        <item x="31"/>
-        <item x="106"/>
-        <item x="216"/>
-        <item x="179"/>
-        <item x="178"/>
-        <item x="376"/>
-        <item x="358"/>
-        <item x="309"/>
-        <item x="355"/>
-        <item x="247"/>
-        <item x="30"/>
-        <item x="17"/>
-        <item x="20"/>
-        <item x="147"/>
-        <item x="274"/>
-        <item x="152"/>
-        <item x="230"/>
-        <item x="27"/>
-        <item x="201"/>
-        <item x="212"/>
-        <item x="220"/>
-        <item x="211"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="245"/>
-        <item x="256"/>
-        <item x="14"/>
-        <item x="67"/>
-        <item x="132"/>
-        <item x="45"/>
-        <item x="267"/>
-        <item x="265"/>
-        <item x="93"/>
-        <item x="313"/>
-        <item x="310"/>
-        <item x="203"/>
-        <item x="130"/>
-        <item x="240"/>
-        <item x="72"/>
-        <item x="63"/>
-        <item x="239"/>
-        <item x="32"/>
-        <item x="34"/>
-        <item x="338"/>
-        <item x="346"/>
-        <item x="296"/>
-        <item x="333"/>
-        <item x="35"/>
-        <item x="365"/>
-        <item x="156"/>
-        <item x="7"/>
-        <item x="47"/>
-        <item x="169"/>
-        <item x="273"/>
-        <item x="98"/>
-        <item x="153"/>
-        <item x="26"/>
-        <item x="292"/>
-        <item x="280"/>
-        <item x="38"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item x="364"/>
-        <item x="206"/>
-        <item x="362"/>
-        <item x="204"/>
-        <item x="122"/>
-        <item x="120"/>
-        <item x="366"/>
-        <item x="61"/>
-        <item x="77"/>
-        <item x="82"/>
-        <item x="168"/>
-        <item x="375"/>
-        <item x="154"/>
-        <item x="223"/>
-        <item x="295"/>
-        <item x="298"/>
-        <item x="59"/>
-        <item x="80"/>
-        <item x="331"/>
-        <item x="94"/>
-        <item x="277"/>
-        <item x="373"/>
-        <item x="157"/>
-        <item x="257"/>
-        <item x="225"/>
-        <item x="369"/>
-        <item x="294"/>
-        <item x="115"/>
-        <item x="209"/>
-        <item x="268"/>
-        <item x="221"/>
-        <item x="367"/>
-        <item x="235"/>
-        <item x="127"/>
-        <item x="320"/>
-        <item x="330"/>
-        <item x="95"/>
-        <item x="193"/>
-        <item x="148"/>
-        <item x="37"/>
-        <item x="215"/>
-        <item x="197"/>
-        <item x="300"/>
-        <item x="258"/>
-        <item x="184"/>
-        <item x="39"/>
-        <item x="261"/>
-        <item x="131"/>
-        <item x="248"/>
-        <item x="287"/>
-        <item x="289"/>
-        <item x="285"/>
-        <item x="263"/>
-        <item x="40"/>
-        <item x="359"/>
-        <item x="231"/>
-        <item x="89"/>
-        <item x="286"/>
-        <item x="272"/>
-        <item x="116"/>
-        <item x="305"/>
-        <item x="100"/>
-        <item x="99"/>
-        <item x="329"/>
-        <item x="12"/>
-        <item x="317"/>
-        <item x="271"/>
-        <item x="136"/>
-        <item x="55"/>
-        <item x="328"/>
-        <item x="84"/>
-        <item x="134"/>
-        <item x="36"/>
-        <item x="353"/>
-        <item x="332"/>
-        <item x="91"/>
-        <item x="11"/>
-        <item x="228"/>
-        <item x="371"/>
-        <item x="170"/>
-        <item x="275"/>
-        <item x="374"/>
-        <item x="142"/>
-        <item x="198"/>
-        <item x="110"/>
-        <item x="109"/>
-        <item x="335"/>
-        <item x="175"/>
-        <item x="135"/>
-        <item x="161"/>
-        <item x="217"/>
-        <item x="174"/>
-        <item x="302"/>
-        <item x="278"/>
-        <item x="180"/>
-        <item x="291"/>
-        <item x="226"/>
-        <item x="260"/>
-        <item x="282"/>
-        <item x="321"/>
-        <item x="6"/>
-        <item x="325"/>
-        <item x="96"/>
-        <item x="48"/>
-        <item x="87"/>
-        <item x="151"/>
-        <item x="172"/>
-        <item x="283"/>
-        <item x="52"/>
-        <item x="57"/>
-        <item x="189"/>
-        <item x="138"/>
-        <item x="236"/>
-        <item x="163"/>
-        <item x="255"/>
-        <item x="253"/>
-        <item x="242"/>
-        <item x="181"/>
-        <item x="21"/>
-        <item x="177"/>
-        <item x="336"/>
-        <item x="207"/>
-        <item x="103"/>
-        <item x="124"/>
-        <item x="251"/>
-        <item x="312"/>
-        <item x="74"/>
-        <item x="71"/>
-        <item x="186"/>
-        <item x="65"/>
-        <item x="218"/>
-        <item x="368"/>
-        <item x="315"/>
-        <item x="288"/>
-        <item x="83"/>
-        <item x="190"/>
-        <item x="360"/>
-        <item x="187"/>
-        <item x="81"/>
-        <item x="214"/>
-        <item x="233"/>
-        <item x="86"/>
-        <item x="129"/>
-        <item x="185"/>
-        <item x="188"/>
-        <item x="56"/>
-        <item x="210"/>
-        <item x="213"/>
-        <item x="297"/>
-        <item x="53"/>
-        <item x="76"/>
-        <item x="54"/>
-        <item x="46"/>
-        <item x="208"/>
-        <item x="44"/>
-        <item x="101"/>
-        <item x="3"/>
-        <item x="243"/>
-        <item x="334"/>
-        <item x="5"/>
-        <item x="112"/>
-        <item x="319"/>
-        <item x="195"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="183"/>
-        <item x="199"/>
-        <item x="301"/>
-        <item x="126"/>
-        <item x="28"/>
-        <item x="299"/>
-        <item x="205"/>
-        <item x="290"/>
-        <item x="314"/>
-        <item x="144"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="22"/>
-        <item x="158"/>
-        <item x="323"/>
-        <item x="348"/>
-        <item x="244"/>
-        <item x="324"/>
-        <item x="118"/>
-        <item x="232"/>
-        <item x="363"/>
-        <item x="149"/>
-        <item x="254"/>
-        <item x="234"/>
-        <item x="196"/>
-        <item x="372"/>
-        <item x="304"/>
-        <item x="73"/>
-        <item x="341"/>
-        <item x="262"/>
-        <item x="224"/>
-        <item x="105"/>
-        <item x="269"/>
-        <item x="113"/>
-        <item x="121"/>
-        <item x="125"/>
-        <item x="58"/>
-        <item x="123"/>
-        <item x="162"/>
-        <item x="24"/>
-        <item x="259"/>
-        <item x="165"/>
-        <item x="326"/>
-        <item x="145"/>
-        <item x="264"/>
-        <item x="307"/>
-        <item x="200"/>
-        <item x="146"/>
-        <item x="29"/>
-        <item x="182"/>
-        <item x="202"/>
-        <item x="92"/>
-        <item x="104"/>
-        <item x="238"/>
-        <item x="354"/>
-        <item x="281"/>
-        <item x="270"/>
-        <item x="356"/>
-        <item x="70"/>
-        <item x="337"/>
-        <item x="249"/>
-        <item x="50"/>
-        <item x="357"/>
-        <item x="344"/>
-        <item x="43"/>
-        <item x="68"/>
-        <item x="318"/>
-        <item x="349"/>
-        <item x="340"/>
-        <item x="266"/>
-        <item x="62"/>
-        <item x="284"/>
-        <item x="79"/>
-        <item x="75"/>
-        <item x="88"/>
-        <item x="60"/>
-        <item x="41"/>
-        <item x="308"/>
-        <item x="166"/>
-        <item x="133"/>
-        <item x="192"/>
-        <item x="351"/>
-        <item x="229"/>
-        <item x="194"/>
-        <item x="42"/>
-        <item x="141"/>
-        <item x="90"/>
-        <item x="140"/>
-        <item x="97"/>
-        <item x="342"/>
-        <item x="128"/>
-        <item x="4"/>
-        <item x="139"/>
-        <item x="143"/>
-        <item x="345"/>
-        <item x="51"/>
-        <item x="137"/>
-        <item x="23"/>
-        <item x="370"/>
-        <item x="173"/>
-        <item x="8"/>
-        <item x="150"/>
-        <item x="0"/>
-        <item x="250"/>
-        <item x="18"/>
-        <item x="347"/>
-        <item x="327"/>
-        <item x="191"/>
-        <item x="13"/>
-        <item x="49"/>
-        <item x="85"/>
-        <item x="164"/>
-        <item x="66"/>
-        <item x="316"/>
-        <item x="10"/>
-        <item x="252"/>
-        <item x="102"/>
-        <item x="246"/>
-        <item x="322"/>
-        <item x="155"/>
-        <item x="222"/>
-        <item x="279"/>
-        <item x="241"/>
-        <item x="64"/>
-        <item x="69"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="14">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="12"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Contagem de cliente" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6532,140 +1669,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312C4CA2-A45D-4086-AD3F-264DFD1ACBAE}">
-  <dimension ref="A3:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="B3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="11">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="11">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="11">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="B11" s="11">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="11">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="B13" s="11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="11">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" s="11">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="B17" s="11">
-        <v>390</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
   <dimension ref="A1:I391"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD794356-7964-4115-AE12-5C227C19C9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8304F9A2-D718-4E7C-9814-8C26B2B0E27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="410">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -1255,6 +1255,9 @@
   </si>
   <si>
     <t>andreza dias gomes</t>
+  </si>
+  <si>
+    <t>SUELENE</t>
   </si>
 </sst>
 </file>
@@ -1292,12 +1295,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1338,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1356,6 +1365,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2979,25 +2993,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+    <row r="60" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="3" t="s">
+      <c r="B60" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3">
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10">
         <v>8</v>
       </c>
     </row>
@@ -3005,11 +3019,11 @@
       <c r="A61" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>82</v>
+      <c r="B61" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>83</v>
@@ -3027,11 +3041,11 @@
       <c r="A62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>82</v>
+      <c r="B62" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>83</v>
@@ -3049,11 +3063,11 @@
       <c r="A63" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>82</v>
+      <c r="B63" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>83</v>
@@ -3071,11 +3085,11 @@
       <c r="A64" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>82</v>
+      <c r="B64" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>83</v>
@@ -3093,11 +3107,11 @@
       <c r="A65" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>82</v>
+      <c r="B65" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>83</v>
@@ -3115,11 +3129,11 @@
       <c r="A66" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>82</v>
+      <c r="B66" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>83</v>
@@ -3137,11 +3151,11 @@
       <c r="A67" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>82</v>
+      <c r="B67" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>83</v>
@@ -3155,25 +3169,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+    <row r="68" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="B68" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3">
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10">
         <v>8</v>
       </c>
     </row>
@@ -3181,11 +3195,11 @@
       <c r="A69" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>82</v>
+      <c r="B69" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>83</v>
@@ -3203,11 +3217,11 @@
       <c r="A70" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>82</v>
+      <c r="B70" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>83</v>
@@ -3225,11 +3239,11 @@
       <c r="A71" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>82</v>
+      <c r="B71" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>83</v>
@@ -3247,11 +3261,11 @@
       <c r="A72" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>82</v>
+      <c r="B72" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>83</v>
@@ -3269,11 +3283,11 @@
       <c r="A73" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>82</v>
+      <c r="B73" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>83</v>
@@ -3291,11 +3305,11 @@
       <c r="A74" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>82</v>
+      <c r="B74" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>83</v>
@@ -3313,11 +3327,11 @@
       <c r="A75" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>82</v>
+      <c r="B75" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>83</v>
@@ -3335,11 +3349,11 @@
       <c r="A76" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>82</v>
+      <c r="B76" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>83</v>
@@ -3357,11 +3371,11 @@
       <c r="A77" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>82</v>
+      <c r="B77" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>83</v>
@@ -3379,11 +3393,11 @@
       <c r="A78" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>82</v>
+      <c r="B78" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>83</v>

--- a/convertidos.xlsx
+++ b/convertidos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\mapa de calor - Copia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8304F9A2-D718-4E7C-9814-8C26B2B0E27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C484079F-AD8E-4682-AF0C-873CB350985B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
+    <workbookView xWindow="1350" yWindow="300" windowWidth="14400" windowHeight="12240" xr2:uid="{64BEFEE6-6E38-4CB7-B0B6-906EAB4976C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="419">
   <si>
     <t xml:space="preserve">Tatiane Moraes dos Santos </t>
   </si>
@@ -1258,6 +1258,33 @@
   </si>
   <si>
     <t>SUELENE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aryadna Andresa Santos Favacho </t>
+  </si>
+  <si>
+    <t>Vitória conceição da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delson conceição dos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edevan conceição da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valdirene conceição dos </t>
+  </si>
+  <si>
+    <t>Cátia Silva do espírito santo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larissa Raimunda Rodrigues da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josielson Silva da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderleia conceição dos Santos </t>
   </si>
 </sst>
 </file>
@@ -1361,15 +1388,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1684,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B4F1DE-5534-4C97-84AB-D8532D79AB56}">
-  <dimension ref="A1:I391"/>
+  <dimension ref="A1:I400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -2993,25 +3020,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
+    <row r="60" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10">
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8">
         <v>8</v>
       </c>
     </row>
@@ -3019,10 +3046,10 @@
       <c r="A61" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -3041,10 +3068,10 @@
       <c r="A62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -3063,10 +3090,10 @@
       <c r="A63" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -3085,10 +3112,10 @@
       <c r="A64" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -3107,10 +3134,10 @@
       <c r="A65" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -3129,10 +3156,10 @@
       <c r="A66" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -3151,10 +3178,10 @@
       <c r="A67" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -3169,25 +3196,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+    <row r="68" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10">
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8">
         <v>8</v>
       </c>
     </row>
@@ -3195,10 +3222,10 @@
       <c r="A69" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -3217,10 +3244,10 @@
       <c r="A70" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -3239,10 +3266,10 @@
       <c r="A71" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -3261,10 +3288,10 @@
       <c r="A72" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -3283,10 +3310,10 @@
       <c r="A73" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -3305,10 +3332,10 @@
       <c r="A74" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -3327,10 +3354,10 @@
       <c r="A75" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -3349,10 +3376,10 @@
       <c r="A76" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -3371,10 +3398,10 @@
       <c r="A77" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -3393,10 +3420,10 @@
       <c r="A78" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -9598,16 +9625,16 @@
       <c r="A375" t="s">
         <v>392</v>
       </c>
-      <c r="B375" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C375" s="7" t="s">
+      <c r="B375" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C375" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E375" s="8" t="s">
+      <c r="E375" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H375">
@@ -9621,16 +9648,16 @@
       <c r="A376" t="s">
         <v>393</v>
       </c>
-      <c r="B376" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C376" s="7" t="s">
+      <c r="B376" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C376" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D376" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E376" s="8" t="s">
+      <c r="E376" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H376">
@@ -9641,16 +9668,16 @@
       <c r="A377" t="s">
         <v>394</v>
       </c>
-      <c r="B377" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C377" s="7" t="s">
+      <c r="B377" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C377" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E377" s="8" t="s">
+      <c r="E377" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H377">
@@ -9664,16 +9691,16 @@
       <c r="A378" t="s">
         <v>395</v>
       </c>
-      <c r="B378" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C378" s="7" t="s">
+      <c r="B378" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C378" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E378" s="8" t="s">
+      <c r="E378" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H378">
@@ -9687,16 +9714,16 @@
       <c r="A379" t="s">
         <v>396</v>
       </c>
-      <c r="B379" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C379" s="7" t="s">
+      <c r="B379" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C379" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D379" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E379" s="8" t="s">
+      <c r="E379" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H379">
@@ -9710,16 +9737,16 @@
       <c r="A380" t="s">
         <v>397</v>
       </c>
-      <c r="B380" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C380" s="7" t="s">
+      <c r="B380" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C380" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E380" s="8" t="s">
+      <c r="E380" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H380">
@@ -9733,16 +9760,16 @@
       <c r="A381" t="s">
         <v>398</v>
       </c>
-      <c r="B381" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C381" s="7" t="s">
+      <c r="B381" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C381" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E381" s="8" t="s">
+      <c r="E381" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H381">
@@ -9756,16 +9783,16 @@
       <c r="A382" t="s">
         <v>399</v>
       </c>
-      <c r="B382" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C382" s="7" t="s">
+      <c r="B382" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C382" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D382" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E382" s="8" t="s">
+      <c r="E382" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H382">
@@ -9779,16 +9806,16 @@
       <c r="A383" t="s">
         <v>400</v>
       </c>
-      <c r="B383" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C383" s="7" t="s">
+      <c r="B383" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C383" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E383" s="8" t="s">
+      <c r="E383" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H383">
@@ -9802,16 +9829,16 @@
       <c r="A384" t="s">
         <v>401</v>
       </c>
-      <c r="B384" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C384" s="7" t="s">
+      <c r="B384" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C384" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D384" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E384" s="8" t="s">
+      <c r="E384" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H384">
@@ -9825,16 +9852,16 @@
       <c r="A385" t="s">
         <v>402</v>
       </c>
-      <c r="B385" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C385" s="7" t="s">
+      <c r="B385" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C385" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D385" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E385" s="8" t="s">
+      <c r="E385" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H385">
@@ -9848,16 +9875,16 @@
       <c r="A386" t="s">
         <v>403</v>
       </c>
-      <c r="B386" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C386" s="7" t="s">
+      <c r="B386" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C386" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D386" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E386" s="8" t="s">
+      <c r="E386" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H386">
@@ -9871,16 +9898,16 @@
       <c r="A387" t="s">
         <v>404</v>
       </c>
-      <c r="B387" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C387" s="7" t="s">
+      <c r="B387" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C387" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D387" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E387" s="8" t="s">
+      <c r="E387" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H387">
@@ -9894,16 +9921,16 @@
       <c r="A388" t="s">
         <v>405</v>
       </c>
-      <c r="B388" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C388" s="7" t="s">
+      <c r="B388" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C388" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D388" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E388" s="8" t="s">
+      <c r="E388" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H388">
@@ -9917,16 +9944,16 @@
       <c r="A389" t="s">
         <v>406</v>
       </c>
-      <c r="B389" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C389" s="7" t="s">
+      <c r="B389" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C389" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D389" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E389" s="8" t="s">
+      <c r="E389" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H389">
@@ -9940,16 +9967,16 @@
       <c r="A390" t="s">
         <v>407</v>
       </c>
-      <c r="B390" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C390" s="7" t="s">
+      <c r="B390" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C390" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D390" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E390" s="8" t="s">
+      <c r="E390" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H390">
@@ -9963,16 +9990,16 @@
       <c r="A391" t="s">
         <v>408</v>
       </c>
-      <c r="B391" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C391" s="7" t="s">
+      <c r="B391" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C391" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D391" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E391" s="8" t="s">
+      <c r="E391" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H391">
@@ -9980,6 +10007,213 @@
       </c>
       <c r="I391">
         <v>46</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>410</v>
+      </c>
+      <c r="B392" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C392" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D392" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E392" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H392">
+        <v>2</v>
+      </c>
+      <c r="I392">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>411</v>
+      </c>
+      <c r="B393" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C393" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E393" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H393">
+        <v>2</v>
+      </c>
+      <c r="I393">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>412</v>
+      </c>
+      <c r="B394" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C394" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E394" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H394">
+        <v>6</v>
+      </c>
+      <c r="I394">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>413</v>
+      </c>
+      <c r="B395" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C395" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D395" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E395" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H395">
+        <v>10</v>
+      </c>
+      <c r="I395">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>414</v>
+      </c>
+      <c r="B396" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C396" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E396" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H396">
+        <v>2</v>
+      </c>
+      <c r="I396">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>415</v>
+      </c>
+      <c r="B397" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C397" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D397" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E397" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H397">
+        <v>6</v>
+      </c>
+      <c r="I397">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>416</v>
+      </c>
+      <c r="B398" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C398" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D398" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E398" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H398">
+        <v>12</v>
+      </c>
+      <c r="I398">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>417</v>
+      </c>
+      <c r="B399" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C399" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D399" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E399" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H399">
+        <v>2</v>
+      </c>
+      <c r="I399">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>418</v>
+      </c>
+      <c r="B400" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C400" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D400" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E400" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H400">
+        <v>2</v>
+      </c>
+      <c r="I400">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
